--- a/translation_dashboard.xlsx
+++ b/translation_dashboard.xlsx
@@ -1,27 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acvcsc-my.sharepoint.com/personal/ancome_acv-csc_be/Documents/Documenten/Privé/pokemVertaling/pokeemerald/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_A3EE90B418D508E14BFB1709D609781989C3D400" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3CC1611-8C7C-4B36-B393-208C5A2381FB}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$746</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$746</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4101" uniqueCount="4101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4147" uniqueCount="4102">
   <si>
     <t>Bestand</t>
   </si>
@@ -65,7 +81,7 @@
     <t>Hoog</t>
   </si>
   <si>
-    <t xml:space="preserve">Enkel namen te vertalen</t>
+    <t>Enkel namen te vertalen</t>
   </si>
   <si>
     <t>trainer_hill.h</t>
@@ -119,7 +135,7 @@
     <t>Hoog</t>
   </si>
   <si>
-    <t xml:space="preserve">Enkel namen te vertalen</t>
+    <t>Enkel namen te vertalen</t>
   </si>
   <si>
     <t>battle_frontier_trainers.h</t>
@@ -149,7 +165,7 @@
     <t>Hoog</t>
   </si>
   <si>
-    <t xml:space="preserve">Hulp PJ</t>
+    <t>Hulp PJ</t>
   </si>
   <si>
     <t>pokedex_entries.h</t>
@@ -197,7 +213,7 @@
     <t>Hoog</t>
   </si>
   <si>
-    <t xml:space="preserve">Deze is echt groot</t>
+    <t>Deze is echt groot</t>
   </si>
   <si>
     <t>pokedex_text.h</t>
@@ -215,7 +231,7 @@
     <t>Hoog</t>
   </si>
   <si>
-    <t xml:space="preserve">Deze is echt groot</t>
+    <t>Deze is echt groot</t>
   </si>
   <si>
     <t>apprentice.inc</t>
@@ -377,7 +393,7 @@
     <t>Hoog</t>
   </si>
   <si>
-    <t xml:space="preserve">Optional, je kan de nicknames van opponents gek maken</t>
+    <t>Optional, je kan de nicknames van opponents gek maken</t>
   </si>
   <si>
     <t>scripts.inc</t>
@@ -458,7 +474,7 @@
     <t>Hoog</t>
   </si>
   <si>
-    <t xml:space="preserve">HEEFT TEKST!</t>
+    <t>HEEFT TEKST!</t>
   </si>
   <si>
     <t>cable_club.inc</t>
@@ -3095,7 +3111,7 @@
     <t>Hoog</t>
   </si>
   <si>
-    <t xml:space="preserve">Dit is de ending van de vertaling :')</t>
+    <t>Dit is de ending van de vertaling :')</t>
   </si>
   <si>
     <t>scripts.inc</t>
@@ -5513,7 +5529,7 @@
     <t>Middel</t>
   </si>
   <si>
-    <t xml:space="preserve">"NAVEL ROCK"' LOCATIE NIET VERTAALD!</t>
+    <t>"NAVEL ROCK"' LOCATIE NIET VERTAALD!</t>
   </si>
   <si>
     <t>scripts.inc</t>
@@ -5849,7 +5865,7 @@
     <t>Middel</t>
   </si>
   <si>
-    <t xml:space="preserve">"NAVEL ROCK"' LOCATIE NIET VERTAALD!</t>
+    <t>"NAVEL ROCK"' LOCATIE NIET VERTAALD!</t>
   </si>
   <si>
     <t>scripts.inc</t>
@@ -12308,60 +12324,65 @@
     <t>Laag</t>
   </si>
   <si>
-    <t xml:space="preserve">Vertaalde tekens</t>
+    <t>Vertaalde tekens</t>
   </si>
   <si>
     <t>Tekens</t>
   </si>
   <si>
-    <t xml:space="preserve">Tekens van Maps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Onvertaalde tekens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Totaal aantal tekens</t>
+    <t>Tekens van Maps</t>
+  </si>
+  <si>
+    <t>Onvertaalde tekens</t>
+  </si>
+  <si>
+    <t>Totaal aantal tekens</t>
   </si>
   <si>
     <t>Vooruitgang</t>
+  </si>
+  <si>
+    <t>Heeft een zin met twee onvertaalde items: harbor mail en burn heal
+Ook Great Ball en Potion
+eronder nog meer, alles van r3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.000000"/>
+      <sz val="10"/>
       <name val="Courier New"/>
     </font>
     <font>
-      <sz val="12.000000"/>
+      <sz val="12"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
-      <sz val="36.000000"/>
+      <sz val="36"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -12379,38 +12400,61 @@
   </fills>
   <borders count="1">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="2" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="2" borderId="0" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="10" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="9" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Procent" xfId="1" builtinId="5"/>
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -12424,12 +12468,12 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="nl-NL"/>
   <c:roundedCorners val="0"/>
-  <mc:AlternateContent>
-    <mc:Choice Requires="c14">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="102"/>
     </mc:Choice>
     <mc:Fallback>
@@ -12464,9 +12508,8 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
-      <c:spPr bwMode="auto">
+      <c:spPr>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -12485,7 +12528,7 @@
     </c:view3D>
     <c:floor>
       <c:thickness val="0"/>
-      <c:spPr bwMode="auto">
+      <c:spPr>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -12497,7 +12540,7 @@
     </c:floor>
     <c:sideWall>
       <c:thickness val="0"/>
-      <c:spPr bwMode="auto">
+      <c:spPr>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -12509,7 +12552,7 @@
     </c:sideWall>
     <c:backWall>
       <c:thickness val="0"/>
-      <c:spPr bwMode="auto">
+      <c:spPr>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -12525,10 +12568,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.033240"/>
-          <c:y val="0.180510"/>
-          <c:w val="0.933510"/>
-          <c:h val="0.715820"/>
+          <c:x val="3.3239999999999999E-2"/>
+          <c:y val="0.18051"/>
+          <c:w val="0.93350999999999995"/>
+          <c:h val="0.71582000000000001"/>
         </c:manualLayout>
       </c:layout>
       <c:pie3DChart>
@@ -12550,7 +12593,7 @@
           <c:dPt>
             <c:idx val="0"/>
             <c:bubble3D val="0"/>
-            <c:spPr bwMode="auto">
+            <c:spPr>
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
@@ -12563,11 +12606,16 @@
                 </a:solidFill>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-D3DC-44DA-A70D-DABA2E000094}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
             <c:bubble3D val="0"/>
-            <c:spPr bwMode="auto">
+            <c:spPr>
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
@@ -12580,6 +12628,11 @@
                 </a:solidFill>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-D3DC-44DA-A70D-DABA2E000094}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -12602,26 +12655,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>2054087</c:v>
+                  <c:v>2115832</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6030823</c:v>
+                  <c:v>5969078</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-D3DC-44DA-A70D-DABA2E000094}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
-          <c:showCatName val="0"/>
           <c:showLeaderLines val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showPercent val="0"/>
-          <c:showSerName val="0"/>
-          <c:showVal val="0"/>
         </c:dLbls>
       </c:pie3DChart>
-      <c:spPr bwMode="auto">
+      <c:spPr>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -12633,9 +12691,8 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
-      <c:spPr bwMode="auto">
+      <c:spPr>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -12670,8 +12727,8 @@
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
-  <c:spPr bwMode="auto">
-    <a:xfrm rot="0">
+  <c:spPr>
+    <a:xfrm>
       <a:off x="152398" y="1247775"/>
       <a:ext cx="3689349" cy="2006598"/>
     </a:xfrm>
@@ -12710,19 +12767,19 @@
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="nl-NL"/>
   <c:roundedCorners val="0"/>
-  <mc:AlternateContent>
-    <mc:Choice Requires="c14">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="102"/>
     </mc:Choice>
     <mc:Fallback>
@@ -12731,9 +12788,8 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
-      <c:spPr bwMode="auto">
+      <c:spPr>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -12744,6 +12800,7 @@
       </c:spPr>
       <c:txPr>
         <a:bodyPr/>
+        <a:lstStyle/>
         <a:p>
           <a:pPr>
             <a:defRPr sz="1400" b="0" spc="0">
@@ -12758,15 +12815,13 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr/>
+          <a:endParaRPr lang="nl-BE"/>
         </a:p>
       </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout/>
-      </c:layout>
+      <c:layout/>
       <c:doughnutChart>
         <c:varyColors val="1"/>
         <c:ser>
@@ -12785,7 +12840,8 @@
           </c:tx>
           <c:dPt>
             <c:idx val="0"/>
-            <c:spPr bwMode="auto">
+            <c:bubble3D val="0"/>
+            <c:spPr>
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
@@ -12798,10 +12854,16 @@
                 </a:solidFill>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-C6A0-4000-9878-8D5C341CE746}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
-            <c:spPr bwMode="auto">
+            <c:bubble3D val="0"/>
+            <c:spPr>
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
@@ -12814,6 +12876,11 @@
                 </a:solidFill>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-C6A0-4000-9878-8D5C341CE746}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -12836,27 +12903,33 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>670891</c:v>
+                  <c:v>717526</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1428345</c:v>
+                  <c:v>1381710</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-C6A0-4000-9878-8D5C341CE746}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
-          <c:showCatName val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showPercent val="0"/>
-          <c:showSerName val="0"/>
-          <c:showVal val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
         <c:firstSliceAng val="0"/>
         <c:holeSize val="75"/>
       </c:doughnutChart>
-      <c:spPr bwMode="auto">
+      <c:spPr>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -12868,9 +12941,8 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
-      <c:spPr bwMode="auto">
+      <c:spPr>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -12905,8 +12977,8 @@
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
-  <c:spPr bwMode="auto">
-    <a:xfrm rot="0" flipH="0" flipV="0">
+  <c:spPr>
+    <a:xfrm>
       <a:off x="3962399" y="1162050"/>
       <a:ext cx="5114925" cy="2501899"/>
     </a:xfrm>
@@ -12928,6 +13000,7 @@
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
+    <a:lstStyle/>
     <a:p>
       <a:pPr>
         <a:defRPr sz="900">
@@ -12939,611 +13012,20 @@
           <a:cs typeface="+mn-cs"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr/>
+      <a:endParaRPr lang="nl-BE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:categoryAxis>
-  <cs:chartArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:dataLabel>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" spc="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr bwMode="auto">
-      <a:prstGeom prst="rect">
-        <a:avLst/>
-      </a:prstGeom>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
-  <xdr:twoCellAnchor editAs="twoCell">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>152398</xdr:colOff>
@@ -13556,16 +13038,22 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>9524</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="238760122" name="Grafiek 238760121"/>
+        <xdr:cNvPr id="238760122" name="Grafiek 238760121">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000BA303B0E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
-      <xdr:xfrm rot="0">
-        <a:off x="152398" y="1247775"/>
-        <a:ext cx="3689349" cy="2006598"/>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -13575,7 +13063,7 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>165099</xdr:colOff>
@@ -13588,16 +13076,22 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>63499</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="366890496" name=""/>
+        <xdr:cNvPr id="366890496" name="Grafiek 366890495">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000004EDE15}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
-      <xdr:xfrm rot="0" flipH="0" flipV="0">
-        <a:off x="3962399" y="1162050"/>
-        <a:ext cx="5114925" cy="2501899"/>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -13610,291 +13104,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <a:themeElements>
     <a:clrScheme name="">
       <a:dk1>
@@ -13946,7 +13157,7 @@
         <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -14049,22 +13260,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:I746"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="24.33203125"/>
-    <col customWidth="1" min="2" max="2" width="56.109375"/>
-    <col customWidth="1" min="3" max="3" width="15.6640625"/>
-    <col customWidth="1" min="4" max="4" width="14"/>
-    <col customWidth="1" min="5" max="5" width="15"/>
-    <col customWidth="1" min="6" max="6" width="13.5546875"/>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
+    <col min="2" max="2" width="56.109375" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14093,7 +13307,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" hidden="1">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -14119,7 +13333,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" hidden="1">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -14142,7 +13356,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" hidden="1">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -14165,7 +13379,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" hidden="1">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -14188,7 +13402,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" hidden="1">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -14214,7 +13428,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" hidden="1">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -14240,7 +13454,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" hidden="1">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -14266,7 +13480,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" hidden="1">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -14289,7 +13503,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" hidden="1">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -14312,7 +13526,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" hidden="1">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -14338,7 +13552,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" hidden="1">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -14364,7 +13578,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" hidden="1">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -14387,7 +13601,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" hidden="1">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -14410,7 +13624,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" hidden="1">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -14433,7 +13647,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" hidden="1">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>79</v>
       </c>
@@ -14456,7 +13670,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" hidden="1">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>84</v>
       </c>
@@ -14479,7 +13693,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" hidden="1">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>89</v>
       </c>
@@ -14502,7 +13716,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="19" hidden="1">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>93</v>
       </c>
@@ -14528,7 +13742,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="20" hidden="1">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>98</v>
       </c>
@@ -14551,7 +13765,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="21" hidden="1">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>103</v>
       </c>
@@ -14574,7 +13788,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="22" hidden="1">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>108</v>
       </c>
@@ -14597,7 +13811,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="23" hidden="1">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>113</v>
       </c>
@@ -14623,7 +13837,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="24" hidden="1">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>119</v>
       </c>
@@ -14649,7 +13863,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="25" hidden="1">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>125</v>
       </c>
@@ -14672,7 +13886,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="26" hidden="1">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>130</v>
       </c>
@@ -14695,7 +13909,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="27" hidden="1">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>135</v>
       </c>
@@ -14718,7 +13932,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="28" hidden="1">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>140</v>
       </c>
@@ -14744,7 +13958,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" hidden="1">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>146</v>
       </c>
@@ -14767,7 +13981,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="30" hidden="1">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>151</v>
       </c>
@@ -14790,7 +14004,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="31" hidden="1">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>156</v>
       </c>
@@ -14816,7 +14030,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="32" hidden="1">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>162</v>
       </c>
@@ -14842,7 +14056,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="33" hidden="1">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>167</v>
       </c>
@@ -14865,7 +14079,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="34" hidden="1">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>172</v>
       </c>
@@ -14888,7 +14102,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="35" hidden="1">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>177</v>
       </c>
@@ -14914,7 +14128,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="36" hidden="1">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>183</v>
       </c>
@@ -14937,7 +14151,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="37" hidden="1">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>188</v>
       </c>
@@ -14960,7 +14174,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="38" hidden="1">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>193</v>
       </c>
@@ -14986,7 +14200,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="39" hidden="1">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>199</v>
       </c>
@@ -15009,7 +14223,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="40" hidden="1">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>204</v>
       </c>
@@ -15035,7 +14249,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="41" hidden="1">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>210</v>
       </c>
@@ -15058,7 +14272,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="42" hidden="1">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>215</v>
       </c>
@@ -15084,7 +14298,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>221</v>
       </c>
@@ -15109,8 +14323,11 @@
       <c r="H43" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="44" hidden="1">
+      <c r="I43" s="7" t="s">
+        <v>4101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>227</v>
       </c>
@@ -15133,7 +14350,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="45" hidden="1">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>232</v>
       </c>
@@ -15156,7 +14373,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="46" hidden="1">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>237</v>
       </c>
@@ -15179,7 +14396,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="47" hidden="1">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>242</v>
       </c>
@@ -15202,7 +14419,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="48" hidden="1">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>247</v>
       </c>
@@ -15225,7 +14442,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="49" hidden="1">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>252</v>
       </c>
@@ -15248,7 +14465,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="50" hidden="1">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>257</v>
       </c>
@@ -15274,7 +14491,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="51" hidden="1">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>263</v>
       </c>
@@ -15300,7 +14517,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="52" hidden="1">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>269</v>
       </c>
@@ -15326,7 +14543,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>275</v>
       </c>
@@ -15352,7 +14569,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="54" hidden="1">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>281</v>
       </c>
@@ -15375,7 +14592,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="55" hidden="1">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>286</v>
       </c>
@@ -15398,7 +14615,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="56" hidden="1">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>291</v>
       </c>
@@ -15421,7 +14638,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="57" hidden="1">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>296</v>
       </c>
@@ -15444,7 +14661,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="58" hidden="1">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>301</v>
       </c>
@@ -15467,7 +14684,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="59" hidden="1">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>306</v>
       </c>
@@ -15490,7 +14707,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="60" hidden="1">
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>311</v>
       </c>
@@ -15513,7 +14730,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="61" hidden="1">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>316</v>
       </c>
@@ -15536,7 +14753,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="62" hidden="1">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>321</v>
       </c>
@@ -15559,7 +14776,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="63" hidden="1">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>326</v>
       </c>
@@ -15582,7 +14799,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="64" hidden="1">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>331</v>
       </c>
@@ -15605,7 +14822,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="65" hidden="1">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>336</v>
       </c>
@@ -15628,7 +14845,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>341</v>
       </c>
@@ -15654,7 +14871,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="67" hidden="1">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>347</v>
       </c>
@@ -15680,7 +14897,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="68" hidden="1">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>353</v>
       </c>
@@ -15703,7 +14920,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="69" hidden="1">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>358</v>
       </c>
@@ -15726,7 +14943,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="70" hidden="1">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>363</v>
       </c>
@@ -15749,7 +14966,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="71" hidden="1">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>368</v>
       </c>
@@ -15772,7 +14989,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="72" hidden="1">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>373</v>
       </c>
@@ -15795,7 +15012,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="73" hidden="1">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>378</v>
       </c>
@@ -15821,7 +15038,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="74" hidden="1">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>384</v>
       </c>
@@ -15844,7 +15061,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="75" hidden="1">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>389</v>
       </c>
@@ -15867,7 +15084,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="76" hidden="1">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>394</v>
       </c>
@@ -15890,7 +15107,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="77" hidden="1">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>399</v>
       </c>
@@ -15913,7 +15130,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="78" hidden="1">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>404</v>
       </c>
@@ -15936,7 +15153,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="79" hidden="1">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>409</v>
       </c>
@@ -15959,7 +15176,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="80" hidden="1">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>414</v>
       </c>
@@ -15982,7 +15199,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="81" hidden="1">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>419</v>
       </c>
@@ -16005,7 +15222,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="82" hidden="1">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>424</v>
       </c>
@@ -16031,7 +15248,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="83" hidden="1">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>430</v>
       </c>
@@ -16054,7 +15271,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="84" hidden="1">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>435</v>
       </c>
@@ -16077,7 +15294,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="85" hidden="1">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>440</v>
       </c>
@@ -16100,7 +15317,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="86" hidden="1">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>445</v>
       </c>
@@ -16126,7 +15343,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="87" hidden="1">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>451</v>
       </c>
@@ -16149,7 +15366,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="88" hidden="1">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>456</v>
       </c>
@@ -16172,7 +15389,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="89" hidden="1">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>461</v>
       </c>
@@ -16198,7 +15415,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="90" hidden="1">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>467</v>
       </c>
@@ -16221,7 +15438,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="91" hidden="1">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>472</v>
       </c>
@@ -16244,7 +15461,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="92" hidden="1">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>477</v>
       </c>
@@ -16267,7 +15484,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="93" hidden="1">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>482</v>
       </c>
@@ -16293,7 +15510,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="94" hidden="1">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>488</v>
       </c>
@@ -16316,7 +15533,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="95" hidden="1">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>493</v>
       </c>
@@ -16339,7 +15556,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="96" hidden="1">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>498</v>
       </c>
@@ -16362,7 +15579,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="97" hidden="1">
+    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>503</v>
       </c>
@@ -16388,7 +15605,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="98" hidden="1">
+    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>509</v>
       </c>
@@ -16411,7 +15628,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="99" hidden="1">
+    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>514</v>
       </c>
@@ -16434,7 +15651,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="100" hidden="1">
+    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>519</v>
       </c>
@@ -16460,7 +15677,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="101" hidden="1">
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>525</v>
       </c>
@@ -16486,7 +15703,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="102" hidden="1">
+    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>531</v>
       </c>
@@ -16509,7 +15726,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="103" hidden="1">
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>536</v>
       </c>
@@ -16532,7 +15749,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="104" hidden="1">
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>541</v>
       </c>
@@ -16555,7 +15772,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="105" hidden="1">
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>546</v>
       </c>
@@ -16581,7 +15798,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="106" hidden="1">
+    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>552</v>
       </c>
@@ -16607,7 +15824,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="107" hidden="1">
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>558</v>
       </c>
@@ -16630,7 +15847,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="108" hidden="1">
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>563</v>
       </c>
@@ -16653,7 +15870,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="109" hidden="1">
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>568</v>
       </c>
@@ -16679,7 +15896,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="110" hidden="1">
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>574</v>
       </c>
@@ -16705,7 +15922,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="111" hidden="1">
+    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>579</v>
       </c>
@@ -16731,7 +15948,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="112" hidden="1">
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>585</v>
       </c>
@@ -16754,7 +15971,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="113" hidden="1">
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>590</v>
       </c>
@@ -16777,7 +15994,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="114" hidden="1">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>595</v>
       </c>
@@ -16800,7 +16017,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="115" hidden="1">
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>600</v>
       </c>
@@ -16823,7 +16040,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="116" hidden="1">
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>605</v>
       </c>
@@ -16846,7 +16063,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>610</v>
       </c>
@@ -16872,7 +16089,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="118" hidden="1">
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>616</v>
       </c>
@@ -16895,7 +16112,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="119" hidden="1">
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>621</v>
       </c>
@@ -16921,7 +16138,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="120" hidden="1">
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>627</v>
       </c>
@@ -16944,7 +16161,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="121" hidden="1">
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>632</v>
       </c>
@@ -16970,7 +16187,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="122" hidden="1">
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>638</v>
       </c>
@@ -16993,7 +16210,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="123" hidden="1">
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>643</v>
       </c>
@@ -17016,7 +16233,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="124" hidden="1">
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>648</v>
       </c>
@@ -17042,7 +16259,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="125" hidden="1">
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>654</v>
       </c>
@@ -17068,7 +16285,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="126" hidden="1">
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>660</v>
       </c>
@@ -17091,7 +16308,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="127" hidden="1">
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>665</v>
       </c>
@@ -17114,7 +16331,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="128" hidden="1">
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>670</v>
       </c>
@@ -17137,7 +16354,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="129" hidden="1">
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>675</v>
       </c>
@@ -17160,7 +16377,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="130" hidden="1">
+    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>680</v>
       </c>
@@ -17186,7 +16403,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="131" hidden="1">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>686</v>
       </c>
@@ -17209,7 +16426,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="132" hidden="1">
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>691</v>
       </c>
@@ -17235,7 +16452,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="133" hidden="1">
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>697</v>
       </c>
@@ -17261,7 +16478,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="134" hidden="1">
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>703</v>
       </c>
@@ -17287,7 +16504,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="135" hidden="1">
+    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>709</v>
       </c>
@@ -17310,7 +16527,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="136" hidden="1">
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>714</v>
       </c>
@@ -17333,7 +16550,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="137" hidden="1">
+    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>719</v>
       </c>
@@ -17359,7 +16576,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="138" hidden="1">
+    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>725</v>
       </c>
@@ -17385,7 +16602,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="139" hidden="1">
+    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>731</v>
       </c>
@@ -17411,7 +16628,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="140" hidden="1">
+    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>736</v>
       </c>
@@ -17437,7 +16654,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="141" hidden="1">
+    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>742</v>
       </c>
@@ -17463,7 +16680,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="142" hidden="1">
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>748</v>
       </c>
@@ -17486,7 +16703,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="143" hidden="1">
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>753</v>
       </c>
@@ -17509,7 +16726,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="144" hidden="1">
+    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>758</v>
       </c>
@@ -17535,7 +16752,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="145" hidden="1">
+    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>763</v>
       </c>
@@ -17561,7 +16778,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="146" hidden="1">
+    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>769</v>
       </c>
@@ -17584,7 +16801,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="147" hidden="1">
+    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>774</v>
       </c>
@@ -17607,7 +16824,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="148" hidden="1">
+    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>779</v>
       </c>
@@ -17630,7 +16847,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="149" hidden="1">
+    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>784</v>
       </c>
@@ -17656,7 +16873,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="150" hidden="1">
+    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>790</v>
       </c>
@@ -17679,7 +16896,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="151" hidden="1">
+    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>795</v>
       </c>
@@ -17702,7 +16919,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="152" hidden="1">
+    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>800</v>
       </c>
@@ -17728,7 +16945,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="153" hidden="1">
+    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>806</v>
       </c>
@@ -17751,7 +16968,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="154" hidden="1">
+    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>811</v>
       </c>
@@ -17777,7 +16994,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="155" hidden="1">
+    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>817</v>
       </c>
@@ -17803,7 +17020,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>823</v>
       </c>
@@ -17829,7 +17046,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="157" hidden="1">
+    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>829</v>
       </c>
@@ -17852,7 +17069,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="158" hidden="1">
+    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>834</v>
       </c>
@@ -17875,7 +17092,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="159" hidden="1">
+    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>839</v>
       </c>
@@ -17898,7 +17115,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="160" hidden="1">
+    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>844</v>
       </c>
@@ -17921,7 +17138,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="161" hidden="1">
+    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>849</v>
       </c>
@@ -17944,7 +17161,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="162" hidden="1">
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>854</v>
       </c>
@@ -17967,7 +17184,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="163" hidden="1">
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>859</v>
       </c>
@@ -17990,7 +17207,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="164" hidden="1">
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>864</v>
       </c>
@@ -18016,7 +17233,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="165" hidden="1">
+    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>870</v>
       </c>
@@ -18039,7 +17256,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="166" hidden="1">
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>875</v>
       </c>
@@ -18065,7 +17282,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="167" hidden="1">
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>881</v>
       </c>
@@ -18091,7 +17308,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="168" hidden="1">
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>887</v>
       </c>
@@ -18114,7 +17331,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>892</v>
       </c>
@@ -18140,7 +17357,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="170" hidden="1">
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>897</v>
       </c>
@@ -18163,7 +17380,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="171" hidden="1">
+    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>902</v>
       </c>
@@ -18186,7 +17403,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="172" hidden="1">
+    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>907</v>
       </c>
@@ -18209,7 +17426,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="173" hidden="1">
+    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>912</v>
       </c>
@@ -18232,7 +17449,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="174" hidden="1">
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>917</v>
       </c>
@@ -18255,7 +17472,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="175" hidden="1">
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>922</v>
       </c>
@@ -18281,7 +17498,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="176" hidden="1">
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>928</v>
       </c>
@@ -18304,7 +17521,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="177" hidden="1">
+    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>933</v>
       </c>
@@ -18330,7 +17547,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="178" hidden="1">
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>939</v>
       </c>
@@ -18353,7 +17570,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="179" hidden="1">
+    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>944</v>
       </c>
@@ -18379,7 +17596,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="180" hidden="1">
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>950</v>
       </c>
@@ -18402,7 +17619,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="181" hidden="1">
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>955</v>
       </c>
@@ -18425,7 +17642,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="182" hidden="1">
+    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>960</v>
       </c>
@@ -18448,7 +17665,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="183" hidden="1">
+    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>965</v>
       </c>
@@ -18474,7 +17691,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="184" hidden="1">
+    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>971</v>
       </c>
@@ -18497,7 +17714,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="185" hidden="1">
+    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>976</v>
       </c>
@@ -18523,7 +17740,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="186" hidden="1">
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>982</v>
       </c>
@@ -18546,7 +17763,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="187" hidden="1">
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>987</v>
       </c>
@@ -18569,7 +17786,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="188" hidden="1">
+    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>992</v>
       </c>
@@ -18595,7 +17812,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="189" hidden="1">
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>998</v>
       </c>
@@ -18618,7 +17835,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="190" hidden="1">
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>1002</v>
       </c>
@@ -18644,7 +17861,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="191" hidden="1">
+    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>1008</v>
       </c>
@@ -18667,7 +17884,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="192" hidden="1">
+    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>1013</v>
       </c>
@@ -18690,7 +17907,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="193" hidden="1">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>1018</v>
       </c>
@@ -18719,7 +17936,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="194" hidden="1">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>1025</v>
       </c>
@@ -18745,7 +17962,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="195" hidden="1">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>1031</v>
       </c>
@@ -18771,7 +17988,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="196" hidden="1">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>1037</v>
       </c>
@@ -18794,7 +18011,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="197" hidden="1">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>1042</v>
       </c>
@@ -18817,7 +18034,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="198" hidden="1">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>1047</v>
       </c>
@@ -18840,7 +18057,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="199" hidden="1">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>1052</v>
       </c>
@@ -18866,7 +18083,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="200" hidden="1">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>1058</v>
       </c>
@@ -18892,7 +18109,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="201" hidden="1">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>1064</v>
       </c>
@@ -18918,7 +18135,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="202" hidden="1">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>1070</v>
       </c>
@@ -18944,7 +18161,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="203" hidden="1">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>1076</v>
       </c>
@@ -18967,7 +18184,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="204" hidden="1">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>1081</v>
       </c>
@@ -18990,7 +18207,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="205" hidden="1">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>1085</v>
       </c>
@@ -19016,7 +18233,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="206" hidden="1">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>1091</v>
       </c>
@@ -19039,7 +18256,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="207" hidden="1">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>1096</v>
       </c>
@@ -19065,7 +18282,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="208" hidden="1">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>1102</v>
       </c>
@@ -19088,7 +18305,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="209" hidden="1">
+    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>1107</v>
       </c>
@@ -19111,7 +18328,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="210" hidden="1">
+    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>1112</v>
       </c>
@@ -19134,7 +18351,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="211" hidden="1">
+    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>1117</v>
       </c>
@@ -19160,7 +18377,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="212" hidden="1">
+    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>1123</v>
       </c>
@@ -19183,7 +18400,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="213" hidden="1">
+    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>1128</v>
       </c>
@@ -19206,7 +18423,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="214" hidden="1">
+    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>1133</v>
       </c>
@@ -19229,7 +18446,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="215" hidden="1">
+    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>1138</v>
       </c>
@@ -19255,7 +18472,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="216" hidden="1">
+    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>1144</v>
       </c>
@@ -19278,7 +18495,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="217" hidden="1">
+    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>1149</v>
       </c>
@@ -19304,7 +18521,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="218" hidden="1">
+    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>1155</v>
       </c>
@@ -19330,7 +18547,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="219" hidden="1">
+    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>1161</v>
       </c>
@@ -19353,7 +18570,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="220" hidden="1">
+    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>1166</v>
       </c>
@@ -19379,7 +18596,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="221" hidden="1">
+    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>1172</v>
       </c>
@@ -19402,7 +18619,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="222" hidden="1">
+    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>1177</v>
       </c>
@@ -19428,7 +18645,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="223" hidden="1">
+    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>1183</v>
       </c>
@@ -19451,7 +18668,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="224" hidden="1">
+    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>1188</v>
       </c>
@@ -19474,7 +18691,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="225" hidden="1">
+    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>1193</v>
       </c>
@@ -19497,7 +18714,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="226" hidden="1">
+    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>1198</v>
       </c>
@@ -19520,7 +18737,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="227" hidden="1">
+    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>1203</v>
       </c>
@@ -19543,7 +18760,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="228" hidden="1">
+    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>1208</v>
       </c>
@@ -19569,7 +18786,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="229" hidden="1">
+    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>1214</v>
       </c>
@@ -19592,7 +18809,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="230" hidden="1">
+    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>1219</v>
       </c>
@@ -19618,7 +18835,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="231" hidden="1">
+    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>1225</v>
       </c>
@@ -19641,7 +18858,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="232" hidden="1">
+    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>1230</v>
       </c>
@@ -19664,7 +18881,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="233" hidden="1">
+    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>1235</v>
       </c>
@@ -19690,7 +18907,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="234" hidden="1">
+    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>1241</v>
       </c>
@@ -19713,7 +18930,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="235" hidden="1">
+    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>1246</v>
       </c>
@@ -19736,7 +18953,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="236" hidden="1">
+    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>1251</v>
       </c>
@@ -19759,7 +18976,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="237" hidden="1">
+    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>1256</v>
       </c>
@@ -19782,7 +18999,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="238" hidden="1">
+    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>1261</v>
       </c>
@@ -19805,7 +19022,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="239" hidden="1">
+    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>1266</v>
       </c>
@@ -19828,7 +19045,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="240" hidden="1">
+    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>1271</v>
       </c>
@@ -19854,7 +19071,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="241" hidden="1">
+    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>1277</v>
       </c>
@@ -19877,7 +19094,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="242" hidden="1">
+    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>1282</v>
       </c>
@@ -19903,7 +19120,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="243" hidden="1">
+    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>1288</v>
       </c>
@@ -19926,7 +19143,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="244" hidden="1">
+    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>1293</v>
       </c>
@@ -19952,7 +19169,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="245" hidden="1">
+    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>1299</v>
       </c>
@@ -19978,7 +19195,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="246" hidden="1">
+    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>1305</v>
       </c>
@@ -20001,7 +19218,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="247" hidden="1">
+    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>1310</v>
       </c>
@@ -20027,7 +19244,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="248" hidden="1">
+    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>1316</v>
       </c>
@@ -20050,7 +19267,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="249" hidden="1">
+    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>1321</v>
       </c>
@@ -20076,7 +19293,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="250" hidden="1">
+    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>1327</v>
       </c>
@@ -20099,7 +19316,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="251" hidden="1">
+    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>1332</v>
       </c>
@@ -20125,7 +19342,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="252" hidden="1">
+    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>1338</v>
       </c>
@@ -20151,7 +19368,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="253" hidden="1">
+    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>1344</v>
       </c>
@@ -20177,7 +19394,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="254" hidden="1">
+    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>1350</v>
       </c>
@@ -20200,7 +19417,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="255" hidden="1">
+    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>1355</v>
       </c>
@@ -20226,7 +19443,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="256" hidden="1">
+    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>1361</v>
       </c>
@@ -20249,7 +19466,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="257" hidden="1">
+    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>1366</v>
       </c>
@@ -20272,7 +19489,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="258" hidden="1">
+    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>1371</v>
       </c>
@@ -20298,7 +19515,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="259" hidden="1">
+    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>1377</v>
       </c>
@@ -20324,7 +19541,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="260" hidden="1">
+    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>1383</v>
       </c>
@@ -20350,7 +19567,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="261" hidden="1">
+    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>1389</v>
       </c>
@@ -20373,7 +19590,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="262" hidden="1">
+    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>1394</v>
       </c>
@@ -20396,7 +19613,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="263" hidden="1">
+    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>1399</v>
       </c>
@@ -20419,7 +19636,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="264" hidden="1">
+    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>1404</v>
       </c>
@@ -20442,7 +19659,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="265" hidden="1">
+    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>1409</v>
       </c>
@@ -20465,7 +19682,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="266" hidden="1">
+    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>1414</v>
       </c>
@@ -20488,7 +19705,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="267" hidden="1">
+    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>1418</v>
       </c>
@@ -20511,7 +19728,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="268" hidden="1">
+    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>1423</v>
       </c>
@@ -20537,7 +19754,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="269" hidden="1">
+    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>1429</v>
       </c>
@@ -20560,7 +19777,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="270" hidden="1">
+    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>1434</v>
       </c>
@@ -20583,7 +19800,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="271" hidden="1">
+    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>1439</v>
       </c>
@@ -20609,7 +19826,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="272" hidden="1">
+    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>1445</v>
       </c>
@@ -20635,7 +19852,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="273" hidden="1">
+    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>1450</v>
       </c>
@@ -20661,7 +19878,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="274" hidden="1">
+    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>1456</v>
       </c>
@@ -20687,7 +19904,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="275" hidden="1">
+    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>1462</v>
       </c>
@@ -20710,7 +19927,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="276" hidden="1">
+    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>1467</v>
       </c>
@@ -20736,7 +19953,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="277" hidden="1">
+    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>1473</v>
       </c>
@@ -20759,7 +19976,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="278" hidden="1">
+    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>1478</v>
       </c>
@@ -20785,7 +20002,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="279" hidden="1">
+    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>1484</v>
       </c>
@@ -20811,7 +20028,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="280" hidden="1">
+    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>1490</v>
       </c>
@@ -20837,7 +20054,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="281" hidden="1">
+    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>1496</v>
       </c>
@@ -20863,7 +20080,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="282" hidden="1">
+    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>1502</v>
       </c>
@@ -20886,7 +20103,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="283" hidden="1">
+    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>1507</v>
       </c>
@@ -20912,7 +20129,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="284" hidden="1">
+    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>1513</v>
       </c>
@@ -20935,7 +20152,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="285" hidden="1">
+    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>1518</v>
       </c>
@@ -20961,7 +20178,7 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="286" hidden="1">
+    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>1524</v>
       </c>
@@ -20987,7 +20204,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="287" hidden="1">
+    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>1530</v>
       </c>
@@ -21013,7 +20230,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="288" hidden="1">
+    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>1536</v>
       </c>
@@ -21036,7 +20253,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="289" hidden="1">
+    <row r="289" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>1541</v>
       </c>
@@ -21062,7 +20279,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="290" hidden="1">
+    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>1547</v>
       </c>
@@ -21085,7 +20302,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="291" hidden="1">
+    <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>1552</v>
       </c>
@@ -21111,7 +20328,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="292" hidden="1">
+    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>1558</v>
       </c>
@@ -21137,7 +20354,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="293" hidden="1">
+    <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>1564</v>
       </c>
@@ -21160,7 +20377,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="294" hidden="1">
+    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>1569</v>
       </c>
@@ -21186,7 +20403,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="295" hidden="1">
+    <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>1575</v>
       </c>
@@ -21212,7 +20429,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="296" hidden="1">
+    <row r="296" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>1581</v>
       </c>
@@ -21238,7 +20455,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="297" hidden="1">
+    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>1587</v>
       </c>
@@ -21261,7 +20478,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="298" hidden="1">
+    <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>1592</v>
       </c>
@@ -21287,7 +20504,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="299" hidden="1">
+    <row r="299" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>1597</v>
       </c>
@@ -21313,7 +20530,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="300" hidden="1">
+    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>1603</v>
       </c>
@@ -21339,7 +20556,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="301" hidden="1">
+    <row r="301" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>1609</v>
       </c>
@@ -21365,7 +20582,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="302" hidden="1">
+    <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>1615</v>
       </c>
@@ -21391,7 +20608,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="303" hidden="1">
+    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>1621</v>
       </c>
@@ -21414,7 +20631,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="304" hidden="1">
+    <row r="304" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>1626</v>
       </c>
@@ -21440,7 +20657,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="305" hidden="1">
+    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>1632</v>
       </c>
@@ -21463,7 +20680,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="306" hidden="1">
+    <row r="306" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>1637</v>
       </c>
@@ -21489,7 +20706,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="307" hidden="1">
+    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>1643</v>
       </c>
@@ -21515,7 +20732,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="308" hidden="1">
+    <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>1649</v>
       </c>
@@ -21541,7 +20758,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="309" hidden="1">
+    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>1655</v>
       </c>
@@ -21567,7 +20784,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="310" hidden="1">
+    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>1661</v>
       </c>
@@ -21593,7 +20810,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="311" hidden="1">
+    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>1667</v>
       </c>
@@ -21619,7 +20836,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="312" hidden="1">
+    <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>1673</v>
       </c>
@@ -21642,7 +20859,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="313" hidden="1">
+    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>1678</v>
       </c>
@@ -21665,7 +20882,7 @@
         <v>1682</v>
       </c>
     </row>
-    <row r="314" hidden="1">
+    <row r="314" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>1683</v>
       </c>
@@ -21691,7 +20908,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="315" hidden="1">
+    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>1689</v>
       </c>
@@ -21717,7 +20934,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="316">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>1695</v>
       </c>
@@ -21743,7 +20960,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="317" hidden="1">
+    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>1701</v>
       </c>
@@ -21766,7 +20983,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="318" hidden="1">
+    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>1706</v>
       </c>
@@ -21792,7 +21009,7 @@
         <v>1711</v>
       </c>
     </row>
-    <row r="319" hidden="1">
+    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>1712</v>
       </c>
@@ -21818,7 +21035,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="320" hidden="1">
+    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>1718</v>
       </c>
@@ -21841,7 +21058,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="321" hidden="1">
+    <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>1723</v>
       </c>
@@ -21867,7 +21084,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="322" hidden="1">
+    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>1729</v>
       </c>
@@ -21893,7 +21110,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="323" hidden="1">
+    <row r="323" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>1735</v>
       </c>
@@ -21916,7 +21133,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="324" hidden="1">
+    <row r="324" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>1740</v>
       </c>
@@ -21939,7 +21156,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="325" hidden="1">
+    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>1745</v>
       </c>
@@ -21962,7 +21179,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="326" hidden="1">
+    <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>1750</v>
       </c>
@@ -21988,7 +21205,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="327" hidden="1">
+    <row r="327" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>1755</v>
       </c>
@@ -22014,7 +21231,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="328" hidden="1">
+    <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>1761</v>
       </c>
@@ -22040,7 +21257,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="329" hidden="1">
+    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>1767</v>
       </c>
@@ -22066,7 +21283,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="330" hidden="1">
+    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>1773</v>
       </c>
@@ -22092,7 +21309,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="331" hidden="1">
+    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>1779</v>
       </c>
@@ -22118,7 +21335,7 @@
         <v>1784</v>
       </c>
     </row>
-    <row r="332" hidden="1">
+    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>1785</v>
       </c>
@@ -22141,7 +21358,7 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="333" hidden="1">
+    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>1790</v>
       </c>
@@ -22167,7 +21384,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="334" hidden="1">
+    <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>1796</v>
       </c>
@@ -22193,7 +21410,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="335" hidden="1">
+    <row r="335" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>1802</v>
       </c>
@@ -22216,7 +21433,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="336" hidden="1">
+    <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>1807</v>
       </c>
@@ -22242,7 +21459,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="337" hidden="1">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>1813</v>
       </c>
@@ -22265,7 +21482,7 @@
         <v>1817</v>
       </c>
     </row>
-    <row r="338" hidden="1">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>1818</v>
       </c>
@@ -22291,7 +21508,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="339" hidden="1">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>1824</v>
       </c>
@@ -22320,7 +21537,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="340" hidden="1">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>1831</v>
       </c>
@@ -22343,7 +21560,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="341" hidden="1">
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>1836</v>
       </c>
@@ -22369,7 +21586,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="342" hidden="1">
+    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>1842</v>
       </c>
@@ -22395,7 +21612,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="343" hidden="1">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>1848</v>
       </c>
@@ -22421,7 +21638,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="344" hidden="1">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>1854</v>
       </c>
@@ -22447,7 +21664,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="345" hidden="1">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>1860</v>
       </c>
@@ -22473,7 +21690,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="346" hidden="1">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>1866</v>
       </c>
@@ -22499,7 +21716,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="347" hidden="1">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>1872</v>
       </c>
@@ -22522,7 +21739,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="348" hidden="1">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>1877</v>
       </c>
@@ -22548,7 +21765,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="349" hidden="1">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>1883</v>
       </c>
@@ -22574,7 +21791,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="350" hidden="1">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>1889</v>
       </c>
@@ -22600,7 +21817,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="351" hidden="1">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>1895</v>
       </c>
@@ -22623,7 +21840,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="352" hidden="1">
+    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>1900</v>
       </c>
@@ -22646,7 +21863,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="353" hidden="1">
+    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>1905</v>
       </c>
@@ -22669,7 +21886,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="354" hidden="1">
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>1909</v>
       </c>
@@ -22692,7 +21909,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="355" hidden="1">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>1914</v>
       </c>
@@ -22715,7 +21932,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="356" hidden="1">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>1919</v>
       </c>
@@ -22741,7 +21958,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="357" hidden="1">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>1925</v>
       </c>
@@ -22767,7 +21984,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="358" hidden="1">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>1931</v>
       </c>
@@ -22790,7 +22007,7 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="359" hidden="1">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>1936</v>
       </c>
@@ -22819,7 +22036,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="360" hidden="1">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>1943</v>
       </c>
@@ -22845,7 +22062,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="361" hidden="1">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>1949</v>
       </c>
@@ -22868,7 +22085,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="362" hidden="1">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>1954</v>
       </c>
@@ -22891,7 +22108,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="363" hidden="1">
+    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>1959</v>
       </c>
@@ -22917,7 +22134,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="364" hidden="1">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>1965</v>
       </c>
@@ -22943,7 +22160,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="365" hidden="1">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>1971</v>
       </c>
@@ -22966,7 +22183,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="366" hidden="1">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>1976</v>
       </c>
@@ -22989,7 +22206,7 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="367" hidden="1">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>1981</v>
       </c>
@@ -23012,7 +22229,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="368" hidden="1">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>1986</v>
       </c>
@@ -23035,7 +22252,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="369" hidden="1">
+    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>1991</v>
       </c>
@@ -23058,7 +22275,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="370">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>1996</v>
       </c>
@@ -23084,7 +22301,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="371" hidden="1">
+    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>2002</v>
       </c>
@@ -23107,7 +22324,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="372" hidden="1">
+    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>2007</v>
       </c>
@@ -23130,7 +22347,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="373" hidden="1">
+    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>2012</v>
       </c>
@@ -23156,7 +22373,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="374" hidden="1">
+    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>2018</v>
       </c>
@@ -23182,7 +22399,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="375" hidden="1">
+    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>2024</v>
       </c>
@@ -23208,7 +22425,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="376" hidden="1">
+    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>2030</v>
       </c>
@@ -23234,7 +22451,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="377" hidden="1">
+    <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>2036</v>
       </c>
@@ -23257,7 +22474,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="378" hidden="1">
+    <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>2041</v>
       </c>
@@ -23280,7 +22497,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="379" hidden="1">
+    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>2046</v>
       </c>
@@ -23306,7 +22523,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="380" hidden="1">
+    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>2052</v>
       </c>
@@ -23329,7 +22546,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="381" hidden="1">
+    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>2057</v>
       </c>
@@ -23352,7 +22569,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="382" hidden="1">
+    <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>2062</v>
       </c>
@@ -23378,7 +22595,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="383" hidden="1">
+    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>2068</v>
       </c>
@@ -23404,7 +22621,7 @@
         <v>2073</v>
       </c>
     </row>
-    <row r="384" hidden="1">
+    <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>2074</v>
       </c>
@@ -23427,7 +22644,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="385" hidden="1">
+    <row r="385" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>2079</v>
       </c>
@@ -23450,7 +22667,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="386" hidden="1">
+    <row r="386" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>2084</v>
       </c>
@@ -23476,7 +22693,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="387" hidden="1">
+    <row r="387" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>2090</v>
       </c>
@@ -23502,7 +22719,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="388" hidden="1">
+    <row r="388" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>2096</v>
       </c>
@@ -23528,7 +22745,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="389" hidden="1">
+    <row r="389" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>2102</v>
       </c>
@@ -23554,7 +22771,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="390" hidden="1">
+    <row r="390" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>2108</v>
       </c>
@@ -23580,7 +22797,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="391" hidden="1">
+    <row r="391" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>2114</v>
       </c>
@@ -23606,7 +22823,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="392" hidden="1">
+    <row r="392" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>2120</v>
       </c>
@@ -23632,7 +22849,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="393" hidden="1">
+    <row r="393" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>2126</v>
       </c>
@@ -23658,7 +22875,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="394" hidden="1">
+    <row r="394" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>2132</v>
       </c>
@@ -23684,7 +22901,7 @@
         <v>2137</v>
       </c>
     </row>
-    <row r="395" hidden="1">
+    <row r="395" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>2138</v>
       </c>
@@ -23707,7 +22924,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="396" hidden="1">
+    <row r="396" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>2143</v>
       </c>
@@ -23730,7 +22947,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="397">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>2148</v>
       </c>
@@ -23756,7 +22973,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="398" hidden="1">
+    <row r="398" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>2154</v>
       </c>
@@ -23782,7 +22999,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="399" hidden="1">
+    <row r="399" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>2160</v>
       </c>
@@ -23805,7 +23022,7 @@
         <v>2164</v>
       </c>
     </row>
-    <row r="400" hidden="1">
+    <row r="400" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>2165</v>
       </c>
@@ -23828,7 +23045,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="401" hidden="1">
+    <row r="401" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>2170</v>
       </c>
@@ -23851,7 +23068,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="402" hidden="1">
+    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>2175</v>
       </c>
@@ -23874,7 +23091,7 @@
         <v>2179</v>
       </c>
     </row>
-    <row r="403" hidden="1">
+    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>2180</v>
       </c>
@@ -23900,7 +23117,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="404">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>2186</v>
       </c>
@@ -23926,7 +23143,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="405" hidden="1">
+    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>2192</v>
       </c>
@@ -23949,7 +23166,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="406">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>2197</v>
       </c>
@@ -23975,7 +23192,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="407" hidden="1">
+    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>2203</v>
       </c>
@@ -23998,7 +23215,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="408" hidden="1">
+    <row r="408" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>2208</v>
       </c>
@@ -24021,7 +23238,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="409" hidden="1">
+    <row r="409" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>2213</v>
       </c>
@@ -24044,7 +23261,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="410" hidden="1">
+    <row r="410" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>2218</v>
       </c>
@@ -24070,7 +23287,7 @@
         <v>2223</v>
       </c>
     </row>
-    <row r="411" hidden="1">
+    <row r="411" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>2224</v>
       </c>
@@ -24093,7 +23310,7 @@
         <v>2228</v>
       </c>
     </row>
-    <row r="412" hidden="1">
+    <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>2229</v>
       </c>
@@ -24116,7 +23333,7 @@
         <v>2233</v>
       </c>
     </row>
-    <row r="413" hidden="1">
+    <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>2234</v>
       </c>
@@ -24139,7 +23356,7 @@
         <v>2238</v>
       </c>
     </row>
-    <row r="414" hidden="1">
+    <row r="414" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>2239</v>
       </c>
@@ -24165,7 +23382,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="415" hidden="1">
+    <row r="415" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>2245</v>
       </c>
@@ -24191,7 +23408,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="416" hidden="1">
+    <row r="416" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>2251</v>
       </c>
@@ -24214,7 +23431,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="417" hidden="1">
+    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>2256</v>
       </c>
@@ -24237,7 +23454,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="418" hidden="1">
+    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>2261</v>
       </c>
@@ -24263,7 +23480,7 @@
         <v>2266</v>
       </c>
     </row>
-    <row r="419" hidden="1">
+    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>2267</v>
       </c>
@@ -24289,7 +23506,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="420" hidden="1">
+    <row r="420" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>2273</v>
       </c>
@@ -24312,7 +23529,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="421">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>2278</v>
       </c>
@@ -24338,7 +23555,7 @@
         <v>2282</v>
       </c>
     </row>
-    <row r="422" hidden="1">
+    <row r="422" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>2283</v>
       </c>
@@ -24361,7 +23578,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="423" hidden="1">
+    <row r="423" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>2288</v>
       </c>
@@ -24387,7 +23604,7 @@
         <v>2293</v>
       </c>
     </row>
-    <row r="424" hidden="1">
+    <row r="424" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>2294</v>
       </c>
@@ -24410,7 +23627,7 @@
         <v>2298</v>
       </c>
     </row>
-    <row r="425" hidden="1">
+    <row r="425" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>2299</v>
       </c>
@@ -24436,7 +23653,7 @@
         <v>2304</v>
       </c>
     </row>
-    <row r="426" hidden="1">
+    <row r="426" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>2305</v>
       </c>
@@ -24459,7 +23676,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="427" hidden="1">
+    <row r="427" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>2310</v>
       </c>
@@ -24482,7 +23699,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="428" hidden="1">
+    <row r="428" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>2315</v>
       </c>
@@ -24508,7 +23725,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="429" hidden="1">
+    <row r="429" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>2321</v>
       </c>
@@ -24534,7 +23751,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="430" hidden="1">
+    <row r="430" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>2327</v>
       </c>
@@ -24560,7 +23777,7 @@
         <v>2332</v>
       </c>
     </row>
-    <row r="431" hidden="1">
+    <row r="431" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>2333</v>
       </c>
@@ -24586,7 +23803,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="432" hidden="1">
+    <row r="432" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>2339</v>
       </c>
@@ -24612,7 +23829,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="433" hidden="1">
+    <row r="433" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>2345</v>
       </c>
@@ -24638,7 +23855,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="434" hidden="1">
+    <row r="434" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>2351</v>
       </c>
@@ -24661,7 +23878,7 @@
         <v>2355</v>
       </c>
     </row>
-    <row r="435" hidden="1">
+    <row r="435" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>2356</v>
       </c>
@@ -24687,7 +23904,7 @@
         <v>2361</v>
       </c>
     </row>
-    <row r="436" hidden="1">
+    <row r="436" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>2362</v>
       </c>
@@ -24713,7 +23930,7 @@
         <v>2367</v>
       </c>
     </row>
-    <row r="437" hidden="1">
+    <row r="437" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>2368</v>
       </c>
@@ -24739,7 +23956,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="438" hidden="1">
+    <row r="438" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>2374</v>
       </c>
@@ -24765,7 +23982,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="439" hidden="1">
+    <row r="439" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>2380</v>
       </c>
@@ -24791,7 +24008,7 @@
         <v>2385</v>
       </c>
     </row>
-    <row r="440" hidden="1">
+    <row r="440" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>2386</v>
       </c>
@@ -24817,7 +24034,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="441" hidden="1">
+    <row r="441" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>2392</v>
       </c>
@@ -24840,7 +24057,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="442" hidden="1">
+    <row r="442" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>2397</v>
       </c>
@@ -24863,7 +24080,7 @@
         <v>2401</v>
       </c>
     </row>
-    <row r="443" hidden="1">
+    <row r="443" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>2402</v>
       </c>
@@ -24889,7 +24106,7 @@
         <v>2407</v>
       </c>
     </row>
-    <row r="444" hidden="1">
+    <row r="444" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>2408</v>
       </c>
@@ -24912,7 +24129,7 @@
         <v>2412</v>
       </c>
     </row>
-    <row r="445" hidden="1">
+    <row r="445" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>2413</v>
       </c>
@@ -24938,7 +24155,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="446" hidden="1">
+    <row r="446" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>2419</v>
       </c>
@@ -24961,7 +24178,7 @@
         <v>2423</v>
       </c>
     </row>
-    <row r="447" hidden="1">
+    <row r="447" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>2424</v>
       </c>
@@ -24987,7 +24204,7 @@
         <v>2429</v>
       </c>
     </row>
-    <row r="448" hidden="1">
+    <row r="448" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>2430</v>
       </c>
@@ -25013,7 +24230,7 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="449" hidden="1">
+    <row r="449" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>2436</v>
       </c>
@@ -25039,7 +24256,7 @@
         <v>2440</v>
       </c>
     </row>
-    <row r="450" hidden="1">
+    <row r="450" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>2441</v>
       </c>
@@ -25065,7 +24282,7 @@
         <v>2446</v>
       </c>
     </row>
-    <row r="451" hidden="1">
+    <row r="451" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>2447</v>
       </c>
@@ -25088,7 +24305,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="452" hidden="1">
+    <row r="452" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>2452</v>
       </c>
@@ -25114,7 +24331,7 @@
         <v>2457</v>
       </c>
     </row>
-    <row r="453" hidden="1">
+    <row r="453" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>2458</v>
       </c>
@@ -25140,7 +24357,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="454" hidden="1">
+    <row r="454" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>2464</v>
       </c>
@@ -25163,7 +24380,7 @@
         <v>2468</v>
       </c>
     </row>
-    <row r="455" hidden="1">
+    <row r="455" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>2469</v>
       </c>
@@ -25186,7 +24403,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="456" hidden="1">
+    <row r="456" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>2474</v>
       </c>
@@ -25212,7 +24429,7 @@
         <v>2479</v>
       </c>
     </row>
-    <row r="457" hidden="1">
+    <row r="457" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>2480</v>
       </c>
@@ -25238,7 +24455,7 @@
         <v>2485</v>
       </c>
     </row>
-    <row r="458" hidden="1">
+    <row r="458" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>2486</v>
       </c>
@@ -25264,7 +24481,7 @@
         <v>2491</v>
       </c>
     </row>
-    <row r="459" hidden="1">
+    <row r="459" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>2492</v>
       </c>
@@ -25290,7 +24507,7 @@
         <v>2497</v>
       </c>
     </row>
-    <row r="460" hidden="1">
+    <row r="460" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>2498</v>
       </c>
@@ -25316,7 +24533,7 @@
         <v>2503</v>
       </c>
     </row>
-    <row r="461" hidden="1">
+    <row r="461" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>2504</v>
       </c>
@@ -25342,7 +24559,7 @@
         <v>2509</v>
       </c>
     </row>
-    <row r="462" hidden="1">
+    <row r="462" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>2510</v>
       </c>
@@ -25365,7 +24582,7 @@
         <v>2514</v>
       </c>
     </row>
-    <row r="463" hidden="1">
+    <row r="463" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>2515</v>
       </c>
@@ -25388,7 +24605,7 @@
         <v>2519</v>
       </c>
     </row>
-    <row r="464" hidden="1">
+    <row r="464" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>2520</v>
       </c>
@@ -25411,7 +24628,7 @@
         <v>2524</v>
       </c>
     </row>
-    <row r="465" hidden="1">
+    <row r="465" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>2525</v>
       </c>
@@ -25437,7 +24654,7 @@
         <v>2530</v>
       </c>
     </row>
-    <row r="466" hidden="1">
+    <row r="466" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>2531</v>
       </c>
@@ -25463,7 +24680,7 @@
         <v>2536</v>
       </c>
     </row>
-    <row r="467" hidden="1">
+    <row r="467" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>2537</v>
       </c>
@@ -25489,7 +24706,7 @@
         <v>2542</v>
       </c>
     </row>
-    <row r="468" hidden="1">
+    <row r="468" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>2543</v>
       </c>
@@ -25515,7 +24732,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="469" hidden="1">
+    <row r="469" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>2549</v>
       </c>
@@ -25538,7 +24755,7 @@
         <v>2553</v>
       </c>
     </row>
-    <row r="470" hidden="1">
+    <row r="470" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>2554</v>
       </c>
@@ -25561,7 +24778,7 @@
         <v>2558</v>
       </c>
     </row>
-    <row r="471" hidden="1">
+    <row r="471" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>2559</v>
       </c>
@@ -25587,7 +24804,7 @@
         <v>2564</v>
       </c>
     </row>
-    <row r="472" hidden="1">
+    <row r="472" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>2565</v>
       </c>
@@ -25610,7 +24827,7 @@
         <v>2569</v>
       </c>
     </row>
-    <row r="473" hidden="1">
+    <row r="473" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>2570</v>
       </c>
@@ -25636,7 +24853,7 @@
         <v>2575</v>
       </c>
     </row>
-    <row r="474" hidden="1">
+    <row r="474" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>2576</v>
       </c>
@@ -25662,7 +24879,7 @@
         <v>2581</v>
       </c>
     </row>
-    <row r="475" hidden="1">
+    <row r="475" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>2582</v>
       </c>
@@ -25688,7 +24905,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="476" hidden="1">
+    <row r="476" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>2588</v>
       </c>
@@ -25714,7 +24931,7 @@
         <v>2593</v>
       </c>
     </row>
-    <row r="477" hidden="1">
+    <row r="477" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>2594</v>
       </c>
@@ -25737,7 +24954,7 @@
         <v>2598</v>
       </c>
     </row>
-    <row r="478" hidden="1">
+    <row r="478" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>2599</v>
       </c>
@@ -25763,7 +24980,7 @@
         <v>2604</v>
       </c>
     </row>
-    <row r="479" hidden="1">
+    <row r="479" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>2605</v>
       </c>
@@ -25789,7 +25006,7 @@
         <v>2609</v>
       </c>
     </row>
-    <row r="480" hidden="1">
+    <row r="480" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>2610</v>
       </c>
@@ -25812,7 +25029,7 @@
         <v>2614</v>
       </c>
     </row>
-    <row r="481" hidden="1">
+    <row r="481" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>2615</v>
       </c>
@@ -25838,7 +25055,7 @@
         <v>2619</v>
       </c>
     </row>
-    <row r="482" hidden="1">
+    <row r="482" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>2620</v>
       </c>
@@ -25861,7 +25078,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="483" hidden="1">
+    <row r="483" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>2625</v>
       </c>
@@ -25884,7 +25101,7 @@
         <v>2629</v>
       </c>
     </row>
-    <row r="484" hidden="1">
+    <row r="484" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>2630</v>
       </c>
@@ -25910,7 +25127,7 @@
         <v>2635</v>
       </c>
     </row>
-    <row r="485" hidden="1">
+    <row r="485" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>2636</v>
       </c>
@@ -25933,7 +25150,7 @@
         <v>2640</v>
       </c>
     </row>
-    <row r="486" hidden="1">
+    <row r="486" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>2641</v>
       </c>
@@ -25959,7 +25176,7 @@
         <v>2646</v>
       </c>
     </row>
-    <row r="487" hidden="1">
+    <row r="487" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>2647</v>
       </c>
@@ -25985,7 +25202,7 @@
         <v>2651</v>
       </c>
     </row>
-    <row r="488" hidden="1">
+    <row r="488" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>2652</v>
       </c>
@@ -26011,7 +25228,7 @@
         <v>2657</v>
       </c>
     </row>
-    <row r="489" hidden="1">
+    <row r="489" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>2658</v>
       </c>
@@ -26034,7 +25251,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="490" hidden="1">
+    <row r="490" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>2663</v>
       </c>
@@ -26060,7 +25277,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="491" hidden="1">
+    <row r="491" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>2669</v>
       </c>
@@ -26086,7 +25303,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="492" hidden="1">
+    <row r="492" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>2675</v>
       </c>
@@ -26109,7 +25326,7 @@
         <v>2679</v>
       </c>
     </row>
-    <row r="493" hidden="1">
+    <row r="493" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>2680</v>
       </c>
@@ -26132,7 +25349,7 @@
         <v>2684</v>
       </c>
     </row>
-    <row r="494" hidden="1">
+    <row r="494" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>2685</v>
       </c>
@@ -26158,7 +25375,7 @@
         <v>2690</v>
       </c>
     </row>
-    <row r="495" hidden="1">
+    <row r="495" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>2691</v>
       </c>
@@ -26181,7 +25398,7 @@
         <v>2695</v>
       </c>
     </row>
-    <row r="496" hidden="1">
+    <row r="496" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>2696</v>
       </c>
@@ -26207,7 +25424,7 @@
         <v>2701</v>
       </c>
     </row>
-    <row r="497" hidden="1">
+    <row r="497" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>2702</v>
       </c>
@@ -26233,7 +25450,7 @@
         <v>2707</v>
       </c>
     </row>
-    <row r="498" hidden="1">
+    <row r="498" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>2708</v>
       </c>
@@ -26259,7 +25476,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="499" hidden="1">
+    <row r="499" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>2714</v>
       </c>
@@ -26282,7 +25499,7 @@
         <v>2718</v>
       </c>
     </row>
-    <row r="500" hidden="1">
+    <row r="500" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>2719</v>
       </c>
@@ -26305,7 +25522,7 @@
         <v>2723</v>
       </c>
     </row>
-    <row r="501" hidden="1">
+    <row r="501" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>2724</v>
       </c>
@@ -26328,7 +25545,7 @@
         <v>2728</v>
       </c>
     </row>
-    <row r="502" hidden="1">
+    <row r="502" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>2729</v>
       </c>
@@ -26354,7 +25571,7 @@
         <v>2734</v>
       </c>
     </row>
-    <row r="503" hidden="1">
+    <row r="503" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>2735</v>
       </c>
@@ -26380,7 +25597,7 @@
         <v>2740</v>
       </c>
     </row>
-    <row r="504">
+    <row r="504" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>2741</v>
       </c>
@@ -26406,7 +25623,7 @@
         <v>2745</v>
       </c>
     </row>
-    <row r="505" hidden="1">
+    <row r="505" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>2746</v>
       </c>
@@ -26432,7 +25649,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="506" hidden="1">
+    <row r="506" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>2751</v>
       </c>
@@ -26455,7 +25672,7 @@
         <v>2755</v>
       </c>
     </row>
-    <row r="507" hidden="1">
+    <row r="507" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>2756</v>
       </c>
@@ -26478,7 +25695,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="508" hidden="1">
+    <row r="508" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>2761</v>
       </c>
@@ -26504,7 +25721,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="509" hidden="1">
+    <row r="509" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>2767</v>
       </c>
@@ -26527,7 +25744,7 @@
         <v>2771</v>
       </c>
     </row>
-    <row r="510" hidden="1">
+    <row r="510" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>2772</v>
       </c>
@@ -26553,7 +25770,7 @@
         <v>2777</v>
       </c>
     </row>
-    <row r="511" hidden="1">
+    <row r="511" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>2778</v>
       </c>
@@ -26576,7 +25793,7 @@
         <v>2782</v>
       </c>
     </row>
-    <row r="512" hidden="1">
+    <row r="512" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>2783</v>
       </c>
@@ -26602,7 +25819,7 @@
         <v>2788</v>
       </c>
     </row>
-    <row r="513" hidden="1">
+    <row r="513" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>2789</v>
       </c>
@@ -26625,7 +25842,7 @@
         <v>2793</v>
       </c>
     </row>
-    <row r="514" hidden="1">
+    <row r="514" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>2794</v>
       </c>
@@ -26651,7 +25868,7 @@
         <v>2799</v>
       </c>
     </row>
-    <row r="515" hidden="1">
+    <row r="515" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>2800</v>
       </c>
@@ -26674,7 +25891,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="516" hidden="1">
+    <row r="516" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>2805</v>
       </c>
@@ -26700,7 +25917,7 @@
         <v>2810</v>
       </c>
     </row>
-    <row r="517" hidden="1">
+    <row r="517" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>2811</v>
       </c>
@@ -26723,7 +25940,7 @@
         <v>2815</v>
       </c>
     </row>
-    <row r="518" hidden="1">
+    <row r="518" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>2816</v>
       </c>
@@ -26746,7 +25963,7 @@
         <v>2820</v>
       </c>
     </row>
-    <row r="519" hidden="1">
+    <row r="519" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>2821</v>
       </c>
@@ -26769,7 +25986,7 @@
         <v>2825</v>
       </c>
     </row>
-    <row r="520" hidden="1">
+    <row r="520" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>2826</v>
       </c>
@@ -26795,7 +26012,7 @@
         <v>2831</v>
       </c>
     </row>
-    <row r="521" hidden="1">
+    <row r="521" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>2832</v>
       </c>
@@ -26821,7 +26038,7 @@
         <v>2837</v>
       </c>
     </row>
-    <row r="522" hidden="1">
+    <row r="522" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>2838</v>
       </c>
@@ -26847,7 +26064,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="523" hidden="1">
+    <row r="523" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>2844</v>
       </c>
@@ -26870,7 +26087,7 @@
         <v>2848</v>
       </c>
     </row>
-    <row r="524" hidden="1">
+    <row r="524" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>2849</v>
       </c>
@@ -26896,7 +26113,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="525" hidden="1">
+    <row r="525" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>2855</v>
       </c>
@@ -26919,7 +26136,7 @@
         <v>2859</v>
       </c>
     </row>
-    <row r="526" hidden="1">
+    <row r="526" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>2860</v>
       </c>
@@ -26945,7 +26162,7 @@
         <v>2865</v>
       </c>
     </row>
-    <row r="527" hidden="1">
+    <row r="527" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>2866</v>
       </c>
@@ -26971,7 +26188,7 @@
         <v>2871</v>
       </c>
     </row>
-    <row r="528" hidden="1">
+    <row r="528" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>2872</v>
       </c>
@@ -26994,7 +26211,7 @@
         <v>2876</v>
       </c>
     </row>
-    <row r="529" hidden="1">
+    <row r="529" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>2877</v>
       </c>
@@ -27017,7 +26234,7 @@
         <v>2881</v>
       </c>
     </row>
-    <row r="530" hidden="1">
+    <row r="530" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>2882</v>
       </c>
@@ -27043,7 +26260,7 @@
         <v>2887</v>
       </c>
     </row>
-    <row r="531" hidden="1">
+    <row r="531" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>2888</v>
       </c>
@@ -27069,7 +26286,7 @@
         <v>2893</v>
       </c>
     </row>
-    <row r="532" hidden="1">
+    <row r="532" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>2894</v>
       </c>
@@ -27095,7 +26312,7 @@
         <v>2899</v>
       </c>
     </row>
-    <row r="533" hidden="1">
+    <row r="533" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>2900</v>
       </c>
@@ -27121,7 +26338,7 @@
         <v>2905</v>
       </c>
     </row>
-    <row r="534" hidden="1">
+    <row r="534" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>2906</v>
       </c>
@@ -27147,7 +26364,7 @@
         <v>2911</v>
       </c>
     </row>
-    <row r="535" hidden="1">
+    <row r="535" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>2912</v>
       </c>
@@ -27173,7 +26390,7 @@
         <v>2917</v>
       </c>
     </row>
-    <row r="536" hidden="1">
+    <row r="536" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>2918</v>
       </c>
@@ -27196,7 +26413,7 @@
         <v>2922</v>
       </c>
     </row>
-    <row r="537" hidden="1">
+    <row r="537" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>2923</v>
       </c>
@@ -27222,7 +26439,7 @@
         <v>2928</v>
       </c>
     </row>
-    <row r="538" hidden="1">
+    <row r="538" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>2929</v>
       </c>
@@ -27245,7 +26462,7 @@
         <v>2933</v>
       </c>
     </row>
-    <row r="539" hidden="1">
+    <row r="539" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>2934</v>
       </c>
@@ -27268,7 +26485,7 @@
         <v>2938</v>
       </c>
     </row>
-    <row r="540" hidden="1">
+    <row r="540" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>2939</v>
       </c>
@@ -27294,7 +26511,7 @@
         <v>2943</v>
       </c>
     </row>
-    <row r="541" hidden="1">
+    <row r="541" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>2944</v>
       </c>
@@ -27320,7 +26537,7 @@
         <v>2949</v>
       </c>
     </row>
-    <row r="542" hidden="1">
+    <row r="542" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>2950</v>
       </c>
@@ -27346,7 +26563,7 @@
         <v>2955</v>
       </c>
     </row>
-    <row r="543" hidden="1">
+    <row r="543" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>2956</v>
       </c>
@@ -27369,7 +26586,7 @@
         <v>2960</v>
       </c>
     </row>
-    <row r="544" hidden="1">
+    <row r="544" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>2961</v>
       </c>
@@ -27395,7 +26612,7 @@
         <v>2966</v>
       </c>
     </row>
-    <row r="545" hidden="1">
+    <row r="545" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>2967</v>
       </c>
@@ -27421,7 +26638,7 @@
         <v>2972</v>
       </c>
     </row>
-    <row r="546" hidden="1">
+    <row r="546" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>2973</v>
       </c>
@@ -27447,7 +26664,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="547" hidden="1">
+    <row r="547" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>2979</v>
       </c>
@@ -27473,7 +26690,7 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="548" hidden="1">
+    <row r="548" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>2985</v>
       </c>
@@ -27496,7 +26713,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="549" hidden="1">
+    <row r="549" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>2990</v>
       </c>
@@ -27522,7 +26739,7 @@
         <v>2995</v>
       </c>
     </row>
-    <row r="550" hidden="1">
+    <row r="550" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>2996</v>
       </c>
@@ -27545,7 +26762,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="551" hidden="1">
+    <row r="551" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>3001</v>
       </c>
@@ -27571,7 +26788,7 @@
         <v>3006</v>
       </c>
     </row>
-    <row r="552" hidden="1">
+    <row r="552" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>3007</v>
       </c>
@@ -27594,7 +26811,7 @@
         <v>3011</v>
       </c>
     </row>
-    <row r="553" hidden="1">
+    <row r="553" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>3012</v>
       </c>
@@ -27617,7 +26834,7 @@
         <v>3016</v>
       </c>
     </row>
-    <row r="554" hidden="1">
+    <row r="554" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>3017</v>
       </c>
@@ -27643,7 +26860,7 @@
         <v>3022</v>
       </c>
     </row>
-    <row r="555" hidden="1">
+    <row r="555" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>3023</v>
       </c>
@@ -27666,7 +26883,7 @@
         <v>3027</v>
       </c>
     </row>
-    <row r="556" hidden="1">
+    <row r="556" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>3028</v>
       </c>
@@ -27692,7 +26909,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="557" hidden="1">
+    <row r="557" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>3034</v>
       </c>
@@ -27718,7 +26935,7 @@
         <v>3039</v>
       </c>
     </row>
-    <row r="558" hidden="1">
+    <row r="558" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>3040</v>
       </c>
@@ -27741,7 +26958,7 @@
         <v>3044</v>
       </c>
     </row>
-    <row r="559" hidden="1">
+    <row r="559" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>3045</v>
       </c>
@@ -27767,7 +26984,7 @@
         <v>3050</v>
       </c>
     </row>
-    <row r="560" hidden="1">
+    <row r="560" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>3051</v>
       </c>
@@ -27793,7 +27010,7 @@
         <v>3056</v>
       </c>
     </row>
-    <row r="561" hidden="1">
+    <row r="561" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>3057</v>
       </c>
@@ -27819,7 +27036,7 @@
         <v>3062</v>
       </c>
     </row>
-    <row r="562" hidden="1">
+    <row r="562" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>3063</v>
       </c>
@@ -27842,7 +27059,7 @@
         <v>3067</v>
       </c>
     </row>
-    <row r="563" hidden="1">
+    <row r="563" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>3068</v>
       </c>
@@ -27865,7 +27082,7 @@
         <v>3072</v>
       </c>
     </row>
-    <row r="564" hidden="1">
+    <row r="564" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>3073</v>
       </c>
@@ -27891,7 +27108,7 @@
         <v>3078</v>
       </c>
     </row>
-    <row r="565" hidden="1">
+    <row r="565" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>3079</v>
       </c>
@@ -27917,7 +27134,7 @@
         <v>3084</v>
       </c>
     </row>
-    <row r="566" hidden="1">
+    <row r="566" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>3085</v>
       </c>
@@ -27943,7 +27160,7 @@
         <v>3089</v>
       </c>
     </row>
-    <row r="567" hidden="1">
+    <row r="567" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>3090</v>
       </c>
@@ -27969,7 +27186,7 @@
         <v>3095</v>
       </c>
     </row>
-    <row r="568" hidden="1">
+    <row r="568" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>3096</v>
       </c>
@@ -27992,7 +27209,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="569" hidden="1">
+    <row r="569" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>3101</v>
       </c>
@@ -28018,7 +27235,7 @@
         <v>3106</v>
       </c>
     </row>
-    <row r="570" hidden="1">
+    <row r="570" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>3107</v>
       </c>
@@ -28044,7 +27261,7 @@
         <v>3112</v>
       </c>
     </row>
-    <row r="571" hidden="1">
+    <row r="571" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>3113</v>
       </c>
@@ -28070,7 +27287,7 @@
         <v>3118</v>
       </c>
     </row>
-    <row r="572" hidden="1">
+    <row r="572" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>3119</v>
       </c>
@@ -28096,7 +27313,7 @@
         <v>3122</v>
       </c>
     </row>
-    <row r="573" hidden="1">
+    <row r="573" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>3123</v>
       </c>
@@ -28122,7 +27339,7 @@
         <v>3128</v>
       </c>
     </row>
-    <row r="574" hidden="1">
+    <row r="574" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>3129</v>
       </c>
@@ -28148,7 +27365,7 @@
         <v>3134</v>
       </c>
     </row>
-    <row r="575" hidden="1">
+    <row r="575" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>3135</v>
       </c>
@@ -28171,7 +27388,7 @@
         <v>3139</v>
       </c>
     </row>
-    <row r="576" hidden="1">
+    <row r="576" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>3140</v>
       </c>
@@ -28197,7 +27414,7 @@
         <v>3145</v>
       </c>
     </row>
-    <row r="577" hidden="1">
+    <row r="577" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>3146</v>
       </c>
@@ -28223,7 +27440,7 @@
         <v>3151</v>
       </c>
     </row>
-    <row r="578" hidden="1">
+    <row r="578" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>3152</v>
       </c>
@@ -28249,7 +27466,7 @@
         <v>3157</v>
       </c>
     </row>
-    <row r="579" hidden="1">
+    <row r="579" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>3158</v>
       </c>
@@ -28275,7 +27492,7 @@
         <v>3163</v>
       </c>
     </row>
-    <row r="580" hidden="1">
+    <row r="580" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>3164</v>
       </c>
@@ -28301,7 +27518,7 @@
         <v>3169</v>
       </c>
     </row>
-    <row r="581" hidden="1">
+    <row r="581" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>3170</v>
       </c>
@@ -28324,7 +27541,7 @@
         <v>3174</v>
       </c>
     </row>
-    <row r="582" hidden="1">
+    <row r="582" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>3175</v>
       </c>
@@ -28347,7 +27564,7 @@
         <v>3179</v>
       </c>
     </row>
-    <row r="583" hidden="1">
+    <row r="583" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>3180</v>
       </c>
@@ -28373,7 +27590,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="584" hidden="1">
+    <row r="584" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>3186</v>
       </c>
@@ -28399,7 +27616,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="585" hidden="1">
+    <row r="585" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>3192</v>
       </c>
@@ -28422,7 +27639,7 @@
         <v>3196</v>
       </c>
     </row>
-    <row r="586" hidden="1">
+    <row r="586" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>3197</v>
       </c>
@@ -28445,7 +27662,7 @@
         <v>3201</v>
       </c>
     </row>
-    <row r="587" hidden="1">
+    <row r="587" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>3202</v>
       </c>
@@ -28468,7 +27685,7 @@
         <v>3206</v>
       </c>
     </row>
-    <row r="588" hidden="1">
+    <row r="588" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>3207</v>
       </c>
@@ -28491,7 +27708,7 @@
         <v>3211</v>
       </c>
     </row>
-    <row r="589" hidden="1">
+    <row r="589" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>3212</v>
       </c>
@@ -28514,7 +27731,7 @@
         <v>3216</v>
       </c>
     </row>
-    <row r="590" hidden="1">
+    <row r="590" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>3217</v>
       </c>
@@ -28537,7 +27754,7 @@
         <v>3221</v>
       </c>
     </row>
-    <row r="591" hidden="1">
+    <row r="591" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>3222</v>
       </c>
@@ -28560,7 +27777,7 @@
         <v>3226</v>
       </c>
     </row>
-    <row r="592" hidden="1">
+    <row r="592" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>3227</v>
       </c>
@@ -28583,7 +27800,7 @@
         <v>3231</v>
       </c>
     </row>
-    <row r="593" hidden="1">
+    <row r="593" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>3232</v>
       </c>
@@ -28606,7 +27823,7 @@
         <v>3236</v>
       </c>
     </row>
-    <row r="594" hidden="1">
+    <row r="594" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>3237</v>
       </c>
@@ -28629,7 +27846,7 @@
         <v>3241</v>
       </c>
     </row>
-    <row r="595" hidden="1">
+    <row r="595" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>3242</v>
       </c>
@@ -28655,7 +27872,7 @@
         <v>3247</v>
       </c>
     </row>
-    <row r="596" hidden="1">
+    <row r="596" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>3248</v>
       </c>
@@ -28678,7 +27895,7 @@
         <v>3252</v>
       </c>
     </row>
-    <row r="597" hidden="1">
+    <row r="597" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>3253</v>
       </c>
@@ -28701,7 +27918,7 @@
         <v>3257</v>
       </c>
     </row>
-    <row r="598" hidden="1">
+    <row r="598" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>3258</v>
       </c>
@@ -28724,7 +27941,7 @@
         <v>3262</v>
       </c>
     </row>
-    <row r="599" hidden="1">
+    <row r="599" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>3263</v>
       </c>
@@ -28747,7 +27964,7 @@
         <v>3267</v>
       </c>
     </row>
-    <row r="600" hidden="1">
+    <row r="600" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>3268</v>
       </c>
@@ -28770,7 +27987,7 @@
         <v>3272</v>
       </c>
     </row>
-    <row r="601" hidden="1">
+    <row r="601" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>3273</v>
       </c>
@@ -28796,7 +28013,7 @@
         <v>3278</v>
       </c>
     </row>
-    <row r="602" hidden="1">
+    <row r="602" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>3279</v>
       </c>
@@ -28819,7 +28036,7 @@
         <v>3283</v>
       </c>
     </row>
-    <row r="603" hidden="1">
+    <row r="603" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>3284</v>
       </c>
@@ -28842,7 +28059,7 @@
         <v>3288</v>
       </c>
     </row>
-    <row r="604" hidden="1">
+    <row r="604" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>3289</v>
       </c>
@@ -28865,7 +28082,7 @@
         <v>3293</v>
       </c>
     </row>
-    <row r="605" hidden="1">
+    <row r="605" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>3294</v>
       </c>
@@ -28888,7 +28105,7 @@
         <v>3298</v>
       </c>
     </row>
-    <row r="606" hidden="1">
+    <row r="606" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>3299</v>
       </c>
@@ -28911,7 +28128,7 @@
         <v>3303</v>
       </c>
     </row>
-    <row r="607" hidden="1">
+    <row r="607" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>3304</v>
       </c>
@@ -28937,7 +28154,7 @@
         <v>3309</v>
       </c>
     </row>
-    <row r="608" hidden="1">
+    <row r="608" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>3310</v>
       </c>
@@ -28963,7 +28180,7 @@
         <v>3315</v>
       </c>
     </row>
-    <row r="609" hidden="1">
+    <row r="609" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>3316</v>
       </c>
@@ -28989,7 +28206,7 @@
         <v>3321</v>
       </c>
     </row>
-    <row r="610" hidden="1">
+    <row r="610" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>3322</v>
       </c>
@@ -29015,7 +28232,7 @@
         <v>3327</v>
       </c>
     </row>
-    <row r="611" hidden="1">
+    <row r="611" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>3328</v>
       </c>
@@ -29041,7 +28258,7 @@
         <v>3333</v>
       </c>
     </row>
-    <row r="612" hidden="1">
+    <row r="612" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>3334</v>
       </c>
@@ -29067,7 +28284,7 @@
         <v>3339</v>
       </c>
     </row>
-    <row r="613" hidden="1">
+    <row r="613" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>3340</v>
       </c>
@@ -29093,7 +28310,7 @@
         <v>3345</v>
       </c>
     </row>
-    <row r="614" hidden="1">
+    <row r="614" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>3346</v>
       </c>
@@ -29116,7 +28333,7 @@
         <v>3350</v>
       </c>
     </row>
-    <row r="615" hidden="1">
+    <row r="615" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>3351</v>
       </c>
@@ -29139,7 +28356,7 @@
         <v>3355</v>
       </c>
     </row>
-    <row r="616" hidden="1">
+    <row r="616" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>3356</v>
       </c>
@@ -29165,7 +28382,7 @@
         <v>3361</v>
       </c>
     </row>
-    <row r="617" hidden="1">
+    <row r="617" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>3362</v>
       </c>
@@ -29188,7 +28405,7 @@
         <v>3366</v>
       </c>
     </row>
-    <row r="618" hidden="1">
+    <row r="618" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>3367</v>
       </c>
@@ -29211,7 +28428,7 @@
         <v>3371</v>
       </c>
     </row>
-    <row r="619" hidden="1">
+    <row r="619" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>3372</v>
       </c>
@@ -29237,7 +28454,7 @@
         <v>3377</v>
       </c>
     </row>
-    <row r="620" hidden="1">
+    <row r="620" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>3378</v>
       </c>
@@ -29263,7 +28480,7 @@
         <v>3383</v>
       </c>
     </row>
-    <row r="621" hidden="1">
+    <row r="621" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>3384</v>
       </c>
@@ -29289,7 +28506,7 @@
         <v>3389</v>
       </c>
     </row>
-    <row r="622" hidden="1">
+    <row r="622" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>3390</v>
       </c>
@@ -29315,7 +28532,7 @@
         <v>3395</v>
       </c>
     </row>
-    <row r="623" hidden="1">
+    <row r="623" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>3396</v>
       </c>
@@ -29338,7 +28555,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="624" hidden="1">
+    <row r="624" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>3401</v>
       </c>
@@ -29364,7 +28581,7 @@
         <v>3406</v>
       </c>
     </row>
-    <row r="625" hidden="1">
+    <row r="625" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>3407</v>
       </c>
@@ -29387,7 +28604,7 @@
         <v>3411</v>
       </c>
     </row>
-    <row r="626" hidden="1">
+    <row r="626" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>3412</v>
       </c>
@@ -29410,7 +28627,7 @@
         <v>3416</v>
       </c>
     </row>
-    <row r="627" hidden="1">
+    <row r="627" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>3417</v>
       </c>
@@ -29436,7 +28653,7 @@
         <v>3422</v>
       </c>
     </row>
-    <row r="628" hidden="1">
+    <row r="628" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>3423</v>
       </c>
@@ -29462,7 +28679,7 @@
         <v>3428</v>
       </c>
     </row>
-    <row r="629" hidden="1">
+    <row r="629" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>3429</v>
       </c>
@@ -29488,7 +28705,7 @@
         <v>3434</v>
       </c>
     </row>
-    <row r="630" hidden="1">
+    <row r="630" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>3435</v>
       </c>
@@ -29511,7 +28728,7 @@
         <v>3439</v>
       </c>
     </row>
-    <row r="631" hidden="1">
+    <row r="631" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>3440</v>
       </c>
@@ -29537,7 +28754,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="632" hidden="1">
+    <row r="632" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>3446</v>
       </c>
@@ -29563,7 +28780,7 @@
         <v>3451</v>
       </c>
     </row>
-    <row r="633" hidden="1">
+    <row r="633" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>3452</v>
       </c>
@@ -29589,7 +28806,7 @@
         <v>3457</v>
       </c>
     </row>
-    <row r="634" hidden="1">
+    <row r="634" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>3458</v>
       </c>
@@ -29615,7 +28832,7 @@
         <v>3463</v>
       </c>
     </row>
-    <row r="635" hidden="1">
+    <row r="635" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>3464</v>
       </c>
@@ -29641,7 +28858,7 @@
         <v>3469</v>
       </c>
     </row>
-    <row r="636" hidden="1">
+    <row r="636" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>3470</v>
       </c>
@@ -29667,7 +28884,7 @@
         <v>3475</v>
       </c>
     </row>
-    <row r="637" hidden="1">
+    <row r="637" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>3476</v>
       </c>
@@ -29693,7 +28910,7 @@
         <v>3481</v>
       </c>
     </row>
-    <row r="638" hidden="1">
+    <row r="638" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>3482</v>
       </c>
@@ -29719,7 +28936,7 @@
         <v>3487</v>
       </c>
     </row>
-    <row r="639" hidden="1">
+    <row r="639" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>3488</v>
       </c>
@@ -29745,7 +28962,7 @@
         <v>3493</v>
       </c>
     </row>
-    <row r="640" hidden="1">
+    <row r="640" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>3494</v>
       </c>
@@ -29771,7 +28988,7 @@
         <v>3499</v>
       </c>
     </row>
-    <row r="641" hidden="1">
+    <row r="641" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>3500</v>
       </c>
@@ -29797,7 +29014,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="642" hidden="1">
+    <row r="642" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>3506</v>
       </c>
@@ -29823,7 +29040,7 @@
         <v>3511</v>
       </c>
     </row>
-    <row r="643" hidden="1">
+    <row r="643" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>3512</v>
       </c>
@@ -29846,7 +29063,7 @@
         <v>3516</v>
       </c>
     </row>
-    <row r="644" hidden="1">
+    <row r="644" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>3517</v>
       </c>
@@ -29869,7 +29086,7 @@
         <v>3521</v>
       </c>
     </row>
-    <row r="645" hidden="1">
+    <row r="645" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>3522</v>
       </c>
@@ -29895,7 +29112,7 @@
         <v>3527</v>
       </c>
     </row>
-    <row r="646" hidden="1">
+    <row r="646" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>3528</v>
       </c>
@@ -29921,7 +29138,7 @@
         <v>3533</v>
       </c>
     </row>
-    <row r="647" hidden="1">
+    <row r="647" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>3534</v>
       </c>
@@ -29944,7 +29161,7 @@
         <v>3538</v>
       </c>
     </row>
-    <row r="648" hidden="1">
+    <row r="648" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>3539</v>
       </c>
@@ -29970,7 +29187,7 @@
         <v>3544</v>
       </c>
     </row>
-    <row r="649" hidden="1">
+    <row r="649" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>3545</v>
       </c>
@@ -29996,7 +29213,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="650" hidden="1">
+    <row r="650" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>3551</v>
       </c>
@@ -30019,7 +29236,7 @@
         <v>3555</v>
       </c>
     </row>
-    <row r="651" hidden="1">
+    <row r="651" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>3556</v>
       </c>
@@ -30045,7 +29262,7 @@
         <v>3561</v>
       </c>
     </row>
-    <row r="652">
+    <row r="652" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>3562</v>
       </c>
@@ -30071,7 +29288,7 @@
         <v>3566</v>
       </c>
     </row>
-    <row r="653" hidden="1">
+    <row r="653" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>3567</v>
       </c>
@@ -30097,7 +29314,7 @@
         <v>3572</v>
       </c>
     </row>
-    <row r="654" hidden="1">
+    <row r="654" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>3573</v>
       </c>
@@ -30120,7 +29337,7 @@
         <v>3577</v>
       </c>
     </row>
-    <row r="655" hidden="1">
+    <row r="655" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>3578</v>
       </c>
@@ -30146,7 +29363,7 @@
         <v>3583</v>
       </c>
     </row>
-    <row r="656" hidden="1">
+    <row r="656" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>3584</v>
       </c>
@@ -30172,7 +29389,7 @@
         <v>3589</v>
       </c>
     </row>
-    <row r="657" hidden="1">
+    <row r="657" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>3590</v>
       </c>
@@ -30195,7 +29412,7 @@
         <v>3594</v>
       </c>
     </row>
-    <row r="658" hidden="1">
+    <row r="658" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>3595</v>
       </c>
@@ -30218,7 +29435,7 @@
         <v>3599</v>
       </c>
     </row>
-    <row r="659" hidden="1">
+    <row r="659" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>3600</v>
       </c>
@@ -30244,7 +29461,7 @@
         <v>3605</v>
       </c>
     </row>
-    <row r="660" hidden="1">
+    <row r="660" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>3606</v>
       </c>
@@ -30270,7 +29487,7 @@
         <v>3611</v>
       </c>
     </row>
-    <row r="661" hidden="1">
+    <row r="661" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>3612</v>
       </c>
@@ -30296,7 +29513,7 @@
         <v>3617</v>
       </c>
     </row>
-    <row r="662" hidden="1">
+    <row r="662" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>3618</v>
       </c>
@@ -30322,7 +29539,7 @@
         <v>3623</v>
       </c>
     </row>
-    <row r="663" hidden="1">
+    <row r="663" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>3624</v>
       </c>
@@ -30348,7 +29565,7 @@
         <v>3629</v>
       </c>
     </row>
-    <row r="664" hidden="1">
+    <row r="664" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>3630</v>
       </c>
@@ -30374,7 +29591,7 @@
         <v>3635</v>
       </c>
     </row>
-    <row r="665" hidden="1">
+    <row r="665" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>3636</v>
       </c>
@@ -30400,7 +29617,7 @@
         <v>3641</v>
       </c>
     </row>
-    <row r="666" hidden="1">
+    <row r="666" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>3642</v>
       </c>
@@ -30426,7 +29643,7 @@
         <v>3647</v>
       </c>
     </row>
-    <row r="667" hidden="1">
+    <row r="667" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
         <v>3648</v>
       </c>
@@ -30452,7 +29669,7 @@
         <v>3653</v>
       </c>
     </row>
-    <row r="668" hidden="1">
+    <row r="668" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>3654</v>
       </c>
@@ -30478,7 +29695,7 @@
         <v>3659</v>
       </c>
     </row>
-    <row r="669" hidden="1">
+    <row r="669" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>3660</v>
       </c>
@@ -30504,7 +29721,7 @@
         <v>3665</v>
       </c>
     </row>
-    <row r="670" hidden="1">
+    <row r="670" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>3666</v>
       </c>
@@ -30527,7 +29744,7 @@
         <v>3670</v>
       </c>
     </row>
-    <row r="671" hidden="1">
+    <row r="671" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>3671</v>
       </c>
@@ -30553,7 +29770,7 @@
         <v>3676</v>
       </c>
     </row>
-    <row r="672" hidden="1">
+    <row r="672" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>3677</v>
       </c>
@@ -30576,7 +29793,7 @@
         <v>3681</v>
       </c>
     </row>
-    <row r="673" hidden="1">
+    <row r="673" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>3682</v>
       </c>
@@ -30599,7 +29816,7 @@
         <v>3686</v>
       </c>
     </row>
-    <row r="674" hidden="1">
+    <row r="674" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>3687</v>
       </c>
@@ -30625,7 +29842,7 @@
         <v>3692</v>
       </c>
     </row>
-    <row r="675" hidden="1">
+    <row r="675" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>3693</v>
       </c>
@@ -30651,7 +29868,7 @@
         <v>3698</v>
       </c>
     </row>
-    <row r="676" hidden="1">
+    <row r="676" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>3699</v>
       </c>
@@ -30677,7 +29894,7 @@
         <v>3704</v>
       </c>
     </row>
-    <row r="677" hidden="1">
+    <row r="677" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>3705</v>
       </c>
@@ -30703,7 +29920,7 @@
         <v>3710</v>
       </c>
     </row>
-    <row r="678" hidden="1">
+    <row r="678" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>3711</v>
       </c>
@@ -30729,7 +29946,7 @@
         <v>3716</v>
       </c>
     </row>
-    <row r="679" hidden="1">
+    <row r="679" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>3717</v>
       </c>
@@ -30755,7 +29972,7 @@
         <v>3722</v>
       </c>
     </row>
-    <row r="680" hidden="1">
+    <row r="680" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>3723</v>
       </c>
@@ -30781,7 +29998,7 @@
         <v>3728</v>
       </c>
     </row>
-    <row r="681" hidden="1">
+    <row r="681" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
         <v>3729</v>
       </c>
@@ -30807,7 +30024,7 @@
         <v>3734</v>
       </c>
     </row>
-    <row r="682" hidden="1">
+    <row r="682" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>3735</v>
       </c>
@@ -30833,7 +30050,7 @@
         <v>3740</v>
       </c>
     </row>
-    <row r="683" hidden="1">
+    <row r="683" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>3741</v>
       </c>
@@ -30859,7 +30076,7 @@
         <v>3746</v>
       </c>
     </row>
-    <row r="684" hidden="1">
+    <row r="684" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>3747</v>
       </c>
@@ -30885,7 +30102,7 @@
         <v>3752</v>
       </c>
     </row>
-    <row r="685" hidden="1">
+    <row r="685" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>3753</v>
       </c>
@@ -30911,7 +30128,7 @@
         <v>3758</v>
       </c>
     </row>
-    <row r="686" hidden="1">
+    <row r="686" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>3759</v>
       </c>
@@ -30937,7 +30154,7 @@
         <v>3764</v>
       </c>
     </row>
-    <row r="687" hidden="1">
+    <row r="687" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>3765</v>
       </c>
@@ -30963,7 +30180,7 @@
         <v>3770</v>
       </c>
     </row>
-    <row r="688" hidden="1">
+    <row r="688" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
         <v>3771</v>
       </c>
@@ -30989,7 +30206,7 @@
         <v>3776</v>
       </c>
     </row>
-    <row r="689" hidden="1">
+    <row r="689" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
         <v>3777</v>
       </c>
@@ -31012,7 +30229,7 @@
         <v>3781</v>
       </c>
     </row>
-    <row r="690" hidden="1">
+    <row r="690" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
         <v>3782</v>
       </c>
@@ -31038,7 +30255,7 @@
         <v>3787</v>
       </c>
     </row>
-    <row r="691" hidden="1">
+    <row r="691" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
         <v>3788</v>
       </c>
@@ -31061,7 +30278,7 @@
         <v>3792</v>
       </c>
     </row>
-    <row r="692" hidden="1">
+    <row r="692" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
         <v>3793</v>
       </c>
@@ -31084,7 +30301,7 @@
         <v>3797</v>
       </c>
     </row>
-    <row r="693" hidden="1">
+    <row r="693" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
         <v>3798</v>
       </c>
@@ -31107,7 +30324,7 @@
         <v>3802</v>
       </c>
     </row>
-    <row r="694" hidden="1">
+    <row r="694" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
         <v>3803</v>
       </c>
@@ -31130,7 +30347,7 @@
         <v>3807</v>
       </c>
     </row>
-    <row r="695" hidden="1">
+    <row r="695" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
         <v>3808</v>
       </c>
@@ -31153,7 +30370,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="696" hidden="1">
+    <row r="696" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
         <v>3813</v>
       </c>
@@ -31176,7 +30393,7 @@
         <v>3817</v>
       </c>
     </row>
-    <row r="697" hidden="1">
+    <row r="697" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
         <v>3818</v>
       </c>
@@ -31199,7 +30416,7 @@
         <v>3822</v>
       </c>
     </row>
-    <row r="698" hidden="1">
+    <row r="698" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
         <v>3823</v>
       </c>
@@ -31222,7 +30439,7 @@
         <v>3827</v>
       </c>
     </row>
-    <row r="699" hidden="1">
+    <row r="699" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
         <v>3828</v>
       </c>
@@ -31245,7 +30462,7 @@
         <v>3832</v>
       </c>
     </row>
-    <row r="700" hidden="1">
+    <row r="700" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
         <v>3833</v>
       </c>
@@ -31268,7 +30485,7 @@
         <v>3837</v>
       </c>
     </row>
-    <row r="701" hidden="1">
+    <row r="701" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
         <v>3838</v>
       </c>
@@ -31291,7 +30508,7 @@
         <v>3842</v>
       </c>
     </row>
-    <row r="702" hidden="1">
+    <row r="702" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
         <v>3843</v>
       </c>
@@ -31314,7 +30531,7 @@
         <v>3847</v>
       </c>
     </row>
-    <row r="703" hidden="1">
+    <row r="703" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
         <v>3848</v>
       </c>
@@ -31337,7 +30554,7 @@
         <v>3852</v>
       </c>
     </row>
-    <row r="704" hidden="1">
+    <row r="704" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
         <v>3853</v>
       </c>
@@ -31360,7 +30577,7 @@
         <v>3857</v>
       </c>
     </row>
-    <row r="705" hidden="1">
+    <row r="705" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
         <v>3858</v>
       </c>
@@ -31383,7 +30600,7 @@
         <v>3862</v>
       </c>
     </row>
-    <row r="706" hidden="1">
+    <row r="706" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
         <v>3863</v>
       </c>
@@ -31406,7 +30623,7 @@
         <v>3867</v>
       </c>
     </row>
-    <row r="707" hidden="1">
+    <row r="707" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
         <v>3868</v>
       </c>
@@ -31429,7 +30646,7 @@
         <v>3872</v>
       </c>
     </row>
-    <row r="708" hidden="1">
+    <row r="708" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
         <v>3873</v>
       </c>
@@ -31452,7 +30669,7 @@
         <v>3877</v>
       </c>
     </row>
-    <row r="709" hidden="1">
+    <row r="709" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
         <v>3878</v>
       </c>
@@ -31475,7 +30692,7 @@
         <v>3882</v>
       </c>
     </row>
-    <row r="710" hidden="1">
+    <row r="710" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
         <v>3883</v>
       </c>
@@ -31501,7 +30718,7 @@
         <v>3888</v>
       </c>
     </row>
-    <row r="711" hidden="1">
+    <row r="711" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
         <v>3889</v>
       </c>
@@ -31527,7 +30744,7 @@
         <v>3894</v>
       </c>
     </row>
-    <row r="712" hidden="1">
+    <row r="712" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
         <v>3895</v>
       </c>
@@ -31553,7 +30770,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="713" hidden="1">
+    <row r="713" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
         <v>3901</v>
       </c>
@@ -31579,7 +30796,7 @@
         <v>3906</v>
       </c>
     </row>
-    <row r="714" hidden="1">
+    <row r="714" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
         <v>3907</v>
       </c>
@@ -31605,7 +30822,7 @@
         <v>3912</v>
       </c>
     </row>
-    <row r="715" hidden="1">
+    <row r="715" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
         <v>3913</v>
       </c>
@@ -31631,7 +30848,7 @@
         <v>3918</v>
       </c>
     </row>
-    <row r="716" hidden="1">
+    <row r="716" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
         <v>3919</v>
       </c>
@@ -31657,7 +30874,7 @@
         <v>3924</v>
       </c>
     </row>
-    <row r="717" hidden="1">
+    <row r="717" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
         <v>3925</v>
       </c>
@@ -31683,7 +30900,7 @@
         <v>3929</v>
       </c>
     </row>
-    <row r="718" hidden="1">
+    <row r="718" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
         <v>3930</v>
       </c>
@@ -31709,7 +30926,7 @@
         <v>3935</v>
       </c>
     </row>
-    <row r="719" hidden="1">
+    <row r="719" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
         <v>3936</v>
       </c>
@@ -31735,7 +30952,7 @@
         <v>3941</v>
       </c>
     </row>
-    <row r="720" hidden="1">
+    <row r="720" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
         <v>3942</v>
       </c>
@@ -31758,7 +30975,7 @@
         <v>3946</v>
       </c>
     </row>
-    <row r="721" hidden="1">
+    <row r="721" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
         <v>3947</v>
       </c>
@@ -31784,7 +31001,7 @@
         <v>3952</v>
       </c>
     </row>
-    <row r="722" hidden="1">
+    <row r="722" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>3953</v>
       </c>
@@ -31810,7 +31027,7 @@
         <v>3958</v>
       </c>
     </row>
-    <row r="723" hidden="1">
+    <row r="723" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>3959</v>
       </c>
@@ -31836,7 +31053,7 @@
         <v>3964</v>
       </c>
     </row>
-    <row r="724" hidden="1">
+    <row r="724" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
         <v>3965</v>
       </c>
@@ -31862,7 +31079,7 @@
         <v>3970</v>
       </c>
     </row>
-    <row r="725" hidden="1">
+    <row r="725" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>3971</v>
       </c>
@@ -31885,7 +31102,7 @@
         <v>3975</v>
       </c>
     </row>
-    <row r="726" hidden="1">
+    <row r="726" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
         <v>3976</v>
       </c>
@@ -31908,7 +31125,7 @@
         <v>3980</v>
       </c>
     </row>
-    <row r="727" hidden="1">
+    <row r="727" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
         <v>3981</v>
       </c>
@@ -31934,7 +31151,7 @@
         <v>3986</v>
       </c>
     </row>
-    <row r="728" hidden="1">
+    <row r="728" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
         <v>3987</v>
       </c>
@@ -31960,7 +31177,7 @@
         <v>3992</v>
       </c>
     </row>
-    <row r="729" hidden="1">
+    <row r="729" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
         <v>3993</v>
       </c>
@@ -31986,7 +31203,7 @@
         <v>3998</v>
       </c>
     </row>
-    <row r="730" hidden="1">
+    <row r="730" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
         <v>3999</v>
       </c>
@@ -32012,7 +31229,7 @@
         <v>4004</v>
       </c>
     </row>
-    <row r="731" hidden="1">
+    <row r="731" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
         <v>4005</v>
       </c>
@@ -32038,7 +31255,7 @@
         <v>4010</v>
       </c>
     </row>
-    <row r="732" hidden="1">
+    <row r="732" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
         <v>4011</v>
       </c>
@@ -32064,7 +31281,7 @@
         <v>4016</v>
       </c>
     </row>
-    <row r="733" hidden="1">
+    <row r="733" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
         <v>4017</v>
       </c>
@@ -32090,7 +31307,7 @@
         <v>4022</v>
       </c>
     </row>
-    <row r="734" hidden="1">
+    <row r="734" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
         <v>4023</v>
       </c>
@@ -32116,7 +31333,7 @@
         <v>4028</v>
       </c>
     </row>
-    <row r="735" hidden="1">
+    <row r="735" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>4029</v>
       </c>
@@ -32142,7 +31359,7 @@
         <v>4034</v>
       </c>
     </row>
-    <row r="736" hidden="1">
+    <row r="736" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>4035</v>
       </c>
@@ -32168,7 +31385,7 @@
         <v>4040</v>
       </c>
     </row>
-    <row r="737" hidden="1">
+    <row r="737" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
         <v>4041</v>
       </c>
@@ -32194,7 +31411,7 @@
         <v>4046</v>
       </c>
     </row>
-    <row r="738" hidden="1">
+    <row r="738" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
         <v>4047</v>
       </c>
@@ -32220,7 +31437,7 @@
         <v>4052</v>
       </c>
     </row>
-    <row r="739" hidden="1">
+    <row r="739" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
         <v>4053</v>
       </c>
@@ -32246,7 +31463,7 @@
         <v>4058</v>
       </c>
     </row>
-    <row r="740" hidden="1">
+    <row r="740" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
         <v>4059</v>
       </c>
@@ -32272,7 +31489,7 @@
         <v>4063</v>
       </c>
     </row>
-    <row r="741" hidden="1">
+    <row r="741" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
         <v>4064</v>
       </c>
@@ -32298,7 +31515,7 @@
         <v>4068</v>
       </c>
     </row>
-    <row r="742" hidden="1">
+    <row r="742" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
         <v>4069</v>
       </c>
@@ -32324,7 +31541,7 @@
         <v>4073</v>
       </c>
     </row>
-    <row r="743" hidden="1">
+    <row r="743" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
         <v>4074</v>
       </c>
@@ -32350,7 +31567,7 @@
         <v>4078</v>
       </c>
     </row>
-    <row r="744" hidden="1">
+    <row r="744" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
         <v>4079</v>
       </c>
@@ -32376,7 +31593,7 @@
         <v>4083</v>
       </c>
     </row>
-    <row r="745" hidden="1">
+    <row r="745" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
         <v>4084</v>
       </c>
@@ -32402,7 +31619,7 @@
         <v>4089</v>
       </c>
     </row>
-    <row r="746" hidden="1">
+    <row r="746" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
         <v>4090</v>
       </c>
@@ -32429,7 +31646,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I746">
+  <autoFilter ref="A1:I746" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
         <filter val="Maps"/>
@@ -32440,68 +31657,35 @@
         <filter val="Route110"/>
       </filters>
     </filterColumn>
-    <sortState ref="A19:I746">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A19:I746">
       <sortCondition descending="1" ref="E1:E746"/>
     </sortState>
   </autoFilter>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{061AB271-0AE9-475E-8B09-BA27DB28D0B5}">
-            <xm:f>"Vertaald"</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FF006100"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFC6EFCE"/>
-                  <bgColor rgb="FFC6EFCE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>G:G</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{011896FE-8F9A-4DFC-B219-8E160B48F730}">
-            <xm:f>"Onvertaald"</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FF9C0006"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>G:G</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
+  <conditionalFormatting sqref="G1:G1048576">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"Vertaald"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"Onvertaald"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="22"/>
-    <col customWidth="1" min="2" max="2" width="25.33203125"/>
-    <col bestFit="1" min="3" max="3" width="9.5546875"/>
-    <col customWidth="1" min="8" max="8" width="18.00390625"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" bestFit="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4095</v>
       </c>
@@ -32522,7 +31706,7 @@
         <v>4097</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4098</v>
       </c>
@@ -32537,19 +31721,19 @@
         <f>SUMIF(Sheet1!G2:G997,"Vertaald",Sheet1!E2:E997)</f>
         <v>2115832</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>734</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="3">
         <f>SUMIFS(Sheet1!E2:E1000,Sheet1!C2:C1000,"Maps",Sheet1!G2:G1000,"Vertaald")</f>
         <v>717526</v>
       </c>
     </row>
-    <row r="3" ht="15">
+    <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4099</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <f>SUM(Sheet1!E2:E997)</f>
         <v>8084910</v>
       </c>
@@ -32560,32 +31744,30 @@
         <f>SUMIF(Sheet1!G2:G997,"Onvertaald",Sheet1!E2:E997)</f>
         <v>5969078</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>4093</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="3">
         <f>SUMIFS(Sheet1!E2:E1000,Sheet1!C2:C1000,"Maps",Sheet1!G2:G1000,"Onvertaald")</f>
         <v>1381710</v>
       </c>
     </row>
-    <row r="4" ht="45">
+    <row r="4" spans="1:8" ht="46.2" x14ac:dyDescent="0.85">
       <c r="A4" s="1" t="s">
         <v>4100</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <f>B1/B3</f>
         <v>0.26170136711478542</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <f>H2/SUM(H2:H3)</f>
         <v>0.34180339895085643</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>